--- a/data/misc./skip_conditions_final.xlsx
+++ b/data/misc./skip_conditions_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/misc./"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFD631F-BA81-1B40-8A93-D92A0F091C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F36F64-DD12-7C44-9732-9E994F3FB7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34560" windowHeight="22340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="80">
   <si>
     <t>State</t>
   </si>
@@ -271,6 +271,9 @@
   <si>
     <t>Data is not available (contacted SecState office, the only have physical ballots bound on site)</t>
   </si>
+  <si>
+    <t>I excluded 2018 state house races because party labels could not be validated consistently. Mississippi special-election candidates were often listed as “Nonpartisan” on the ballot, but benchmark data inconsistently assigned some candidates to Democrat/Republican and others to Nonpartisan/Other, even when real-world party affiliations were known. This made the party-level benchmark unreliable and produced inflated “Other” vote share estimates.</t>
+  </si>
 </sst>
 </file>
 
@@ -313,98 +316,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -732,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E803"/>
+  <dimension ref="A1:E805"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="25" customWidth="1"/>
@@ -7969,16 +7889,16 @@
         <v>43</v>
       </c>
       <c r="B426">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C426" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D426" t="b">
         <v>1</v>
       </c>
-      <c r="E426" t="s">
-        <v>73</v>
+      <c r="E426" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.2">
@@ -7986,16 +7906,16 @@
         <v>43</v>
       </c>
       <c r="B427">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C427" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D427" t="b">
         <v>1</v>
       </c>
-      <c r="E427" t="s">
-        <v>73</v>
+      <c r="E427" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.2">
@@ -8003,7 +7923,7 @@
         <v>43</v>
       </c>
       <c r="B428">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C428" t="s">
         <v>8</v>
@@ -8012,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="E428" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.2">
@@ -8020,7 +7940,7 @@
         <v>43</v>
       </c>
       <c r="B429">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C429" t="s">
         <v>27</v>
@@ -8029,18 +7949,18 @@
         <v>1</v>
       </c>
       <c r="E429" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B430">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C430" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D430" t="b">
         <v>1</v>
@@ -8051,13 +7971,13 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B431">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C431" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D431" t="b">
         <v>1</v>
@@ -8074,7 +7994,7 @@
         <v>2010</v>
       </c>
       <c r="C432" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D432" t="b">
         <v>1</v>
@@ -8091,7 +8011,7 @@
         <v>2010</v>
       </c>
       <c r="C433" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D433" t="b">
         <v>1</v>
@@ -8105,10 +8025,10 @@
         <v>44</v>
       </c>
       <c r="B434">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C434" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D434" t="b">
         <v>1</v>
@@ -8122,10 +8042,10 @@
         <v>44</v>
       </c>
       <c r="B435">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C435" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D435" t="b">
         <v>1</v>
@@ -8142,7 +8062,7 @@
         <v>2014</v>
       </c>
       <c r="C436" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D436" t="b">
         <v>1</v>
@@ -8159,7 +8079,7 @@
         <v>2014</v>
       </c>
       <c r="C437" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D437" t="b">
         <v>1</v>
@@ -8170,13 +8090,13 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B438">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C438" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D438" t="b">
         <v>1</v>
@@ -8187,13 +8107,13 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B439">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C439" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D439" t="b">
         <v>1</v>
@@ -8210,7 +8130,7 @@
         <v>2010</v>
       </c>
       <c r="C440" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D440" t="b">
         <v>1</v>
@@ -8227,7 +8147,7 @@
         <v>2010</v>
       </c>
       <c r="C441" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D441" t="b">
         <v>1</v>
@@ -8241,10 +8161,10 @@
         <v>45</v>
       </c>
       <c r="B442">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C442" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D442" t="b">
         <v>1</v>
@@ -8258,10 +8178,10 @@
         <v>45</v>
       </c>
       <c r="B443">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C443" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D443" t="b">
         <v>1</v>
@@ -8278,7 +8198,7 @@
         <v>2014</v>
       </c>
       <c r="C444" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D444" t="b">
         <v>1</v>
@@ -8295,7 +8215,7 @@
         <v>2014</v>
       </c>
       <c r="C445" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D445" t="b">
         <v>1</v>
@@ -8306,36 +8226,36 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B446">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C446" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D446" t="b">
         <v>1</v>
       </c>
       <c r="E446" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B447">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C447" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D447" t="b">
         <v>1</v>
       </c>
       <c r="E447" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.2">
@@ -8343,7 +8263,7 @@
         <v>46</v>
       </c>
       <c r="B448">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C448" t="s">
         <v>6</v>
@@ -8352,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="E448" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.2">
@@ -8360,7 +8280,7 @@
         <v>46</v>
       </c>
       <c r="B449">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C449" t="s">
         <v>26</v>
@@ -8369,7 +8289,7 @@
         <v>1</v>
       </c>
       <c r="E449" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.2">
@@ -8377,7 +8297,7 @@
         <v>46</v>
       </c>
       <c r="B450">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C450" t="s">
         <v>6</v>
@@ -8386,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="E450" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.2">
@@ -8394,7 +8314,7 @@
         <v>46</v>
       </c>
       <c r="B451">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C451" t="s">
         <v>26</v>
@@ -8403,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="E451" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.2">
@@ -8414,13 +8334,13 @@
         <v>2010</v>
       </c>
       <c r="C452" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D452" t="b">
         <v>1</v>
       </c>
       <c r="E452" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.2">
@@ -8431,13 +8351,13 @@
         <v>2010</v>
       </c>
       <c r="C453" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D453" t="b">
         <v>1</v>
       </c>
       <c r="E453" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.2">
@@ -8445,16 +8365,16 @@
         <v>46</v>
       </c>
       <c r="B454">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C454" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D454" t="b">
         <v>1</v>
       </c>
       <c r="E454" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.2">
@@ -8462,16 +8382,16 @@
         <v>46</v>
       </c>
       <c r="B455">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C455" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D455" t="b">
         <v>1</v>
       </c>
       <c r="E455" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.2">
@@ -8482,7 +8402,7 @@
         <v>2012</v>
       </c>
       <c r="C456" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D456" t="b">
         <v>1</v>
@@ -8499,7 +8419,7 @@
         <v>2012</v>
       </c>
       <c r="C457" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D457" t="b">
         <v>1</v>
@@ -8516,7 +8436,7 @@
         <v>2012</v>
       </c>
       <c r="C458" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D458" t="b">
         <v>1</v>
@@ -8533,7 +8453,7 @@
         <v>2012</v>
       </c>
       <c r="C459" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D459" t="b">
         <v>1</v>
@@ -8547,7 +8467,7 @@
         <v>46</v>
       </c>
       <c r="B460">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C460" t="s">
         <v>6</v>
@@ -8556,7 +8476,7 @@
         <v>1</v>
       </c>
       <c r="E460" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.2">
@@ -8564,7 +8484,7 @@
         <v>46</v>
       </c>
       <c r="B461">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C461" t="s">
         <v>26</v>
@@ -8573,7 +8493,7 @@
         <v>1</v>
       </c>
       <c r="E461" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.2">
@@ -8581,16 +8501,16 @@
         <v>46</v>
       </c>
       <c r="B462">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C462" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D462" t="b">
         <v>1</v>
       </c>
       <c r="E462" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.2">
@@ -8598,16 +8518,16 @@
         <v>46</v>
       </c>
       <c r="B463">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C463" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D463" t="b">
         <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.2">
@@ -8618,7 +8538,7 @@
         <v>2016</v>
       </c>
       <c r="C464" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D464" t="b">
         <v>1</v>
@@ -8635,7 +8555,7 @@
         <v>2016</v>
       </c>
       <c r="C465" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D465" t="b">
         <v>1</v>
@@ -8652,7 +8572,7 @@
         <v>2016</v>
       </c>
       <c r="C466" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D466" t="b">
         <v>1</v>
@@ -8669,7 +8589,7 @@
         <v>2016</v>
       </c>
       <c r="C467" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D467" t="b">
         <v>1</v>
@@ -8683,7 +8603,7 @@
         <v>46</v>
       </c>
       <c r="B468">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C468" t="s">
         <v>6</v>
@@ -8692,7 +8612,7 @@
         <v>1</v>
       </c>
       <c r="E468" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.2">
@@ -8700,7 +8620,7 @@
         <v>46</v>
       </c>
       <c r="B469">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C469" t="s">
         <v>26</v>
@@ -8709,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="E469" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.2">
@@ -8717,7 +8637,7 @@
         <v>46</v>
       </c>
       <c r="B470">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C470" t="s">
         <v>6</v>
@@ -8726,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="E470" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.2">
@@ -8734,7 +8654,7 @@
         <v>46</v>
       </c>
       <c r="B471">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C471" t="s">
         <v>26</v>
@@ -8743,7 +8663,7 @@
         <v>1</v>
       </c>
       <c r="E471" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.2">
@@ -8751,7 +8671,7 @@
         <v>46</v>
       </c>
       <c r="B472">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C472" t="s">
         <v>6</v>
@@ -8760,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="E472" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.2">
@@ -8768,7 +8688,7 @@
         <v>46</v>
       </c>
       <c r="B473">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C473" t="s">
         <v>26</v>
@@ -8777,41 +8697,41 @@
         <v>1</v>
       </c>
       <c r="E473" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B474">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C474" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D474" t="b">
         <v>1</v>
       </c>
       <c r="E474" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B475">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C475" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D475" t="b">
         <v>1</v>
       </c>
       <c r="E475" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.2">
@@ -8822,7 +8742,7 @@
         <v>2012</v>
       </c>
       <c r="C476" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D476" t="b">
         <v>1</v>
@@ -8839,7 +8759,7 @@
         <v>2012</v>
       </c>
       <c r="C477" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D477" t="b">
         <v>1</v>
@@ -8853,10 +8773,10 @@
         <v>48</v>
       </c>
       <c r="B478">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C478" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D478" t="b">
         <v>1</v>
@@ -8870,10 +8790,10 @@
         <v>48</v>
       </c>
       <c r="B479">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C479" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D479" t="b">
         <v>1</v>
@@ -8890,7 +8810,7 @@
         <v>2016</v>
       </c>
       <c r="C480" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D480" t="b">
         <v>1</v>
@@ -8907,7 +8827,7 @@
         <v>2016</v>
       </c>
       <c r="C481" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D481" t="b">
         <v>1</v>
@@ -8918,36 +8838,36 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B482">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C482" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D482" t="b">
         <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B483">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C483" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D483" t="b">
         <v>1</v>
       </c>
       <c r="E483" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.2">
@@ -8958,13 +8878,13 @@
         <v>2006</v>
       </c>
       <c r="C484" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D484" t="b">
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.2">
@@ -8975,13 +8895,13 @@
         <v>2006</v>
       </c>
       <c r="C485" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D485" t="b">
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.2">
@@ -8989,16 +8909,16 @@
         <v>49</v>
       </c>
       <c r="B486">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C486" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D486" t="b">
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.2">
@@ -9006,16 +8926,16 @@
         <v>49</v>
       </c>
       <c r="B487">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C487" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D487" t="b">
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.2">
@@ -9026,13 +8946,13 @@
         <v>2010</v>
       </c>
       <c r="C488" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D488" t="b">
         <v>1</v>
       </c>
       <c r="E488" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.2">
@@ -9043,13 +8963,13 @@
         <v>2010</v>
       </c>
       <c r="C489" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D489" t="b">
         <v>1</v>
       </c>
       <c r="E489" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.2">
@@ -9057,16 +8977,16 @@
         <v>49</v>
       </c>
       <c r="B490">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C490" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D490" t="b">
         <v>1</v>
       </c>
       <c r="E490" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.2">
@@ -9074,16 +8994,16 @@
         <v>49</v>
       </c>
       <c r="B491">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C491" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D491" t="b">
         <v>1</v>
       </c>
       <c r="E491" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.2">
@@ -9094,13 +9014,13 @@
         <v>2012</v>
       </c>
       <c r="C492" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D492" t="b">
         <v>1</v>
       </c>
       <c r="E492" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.2">
@@ -9111,13 +9031,13 @@
         <v>2012</v>
       </c>
       <c r="C493" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D493" t="b">
         <v>1</v>
       </c>
       <c r="E493" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.2">
@@ -9125,16 +9045,16 @@
         <v>49</v>
       </c>
       <c r="B494">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C494" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D494" t="b">
         <v>1</v>
       </c>
       <c r="E494" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.2">
@@ -9142,16 +9062,16 @@
         <v>49</v>
       </c>
       <c r="B495">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C495" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D495" t="b">
         <v>1</v>
       </c>
       <c r="E495" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.2">
@@ -9162,13 +9082,13 @@
         <v>2014</v>
       </c>
       <c r="C496" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D496" t="b">
         <v>1</v>
       </c>
       <c r="E496" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.2">
@@ -9179,13 +9099,13 @@
         <v>2014</v>
       </c>
       <c r="C497" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D497" t="b">
         <v>1</v>
       </c>
       <c r="E497" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.2">
@@ -9193,16 +9113,16 @@
         <v>49</v>
       </c>
       <c r="B498">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C498" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D498" t="b">
         <v>1</v>
       </c>
       <c r="E498" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.2">
@@ -9210,16 +9130,16 @@
         <v>49</v>
       </c>
       <c r="B499">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C499" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D499" t="b">
         <v>1</v>
       </c>
       <c r="E499" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.2">
@@ -9230,13 +9150,13 @@
         <v>2016</v>
       </c>
       <c r="C500" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D500" t="b">
         <v>1</v>
       </c>
       <c r="E500" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.2">
@@ -9247,24 +9167,24 @@
         <v>2016</v>
       </c>
       <c r="C501" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D501" t="b">
         <v>1</v>
       </c>
       <c r="E501" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B502">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C502" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D502" t="b">
         <v>1</v>
@@ -9275,13 +9195,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B503">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C503" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D503" t="b">
         <v>1</v>
@@ -9298,7 +9218,7 @@
         <v>2008</v>
       </c>
       <c r="C504" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D504" t="b">
         <v>1</v>
@@ -9315,7 +9235,7 @@
         <v>2008</v>
       </c>
       <c r="C505" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D505" t="b">
         <v>1</v>
@@ -9329,16 +9249,16 @@
         <v>50</v>
       </c>
       <c r="B506">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C506" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D506" t="b">
         <v>1</v>
       </c>
       <c r="E506" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.2">
@@ -9346,16 +9266,16 @@
         <v>50</v>
       </c>
       <c r="B507">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C507" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D507" t="b">
         <v>1</v>
       </c>
       <c r="E507" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.2">
@@ -9366,7 +9286,7 @@
         <v>2010</v>
       </c>
       <c r="C508" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D508" t="b">
         <v>1</v>
@@ -9383,7 +9303,7 @@
         <v>2010</v>
       </c>
       <c r="C509" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D509" t="b">
         <v>1</v>
@@ -9400,13 +9320,13 @@
         <v>2010</v>
       </c>
       <c r="C510" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D510" t="b">
         <v>1</v>
       </c>
       <c r="E510" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.2">
@@ -9417,13 +9337,13 @@
         <v>2010</v>
       </c>
       <c r="C511" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D511" t="b">
         <v>1</v>
       </c>
       <c r="E511" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.2">
@@ -9434,7 +9354,7 @@
         <v>2010</v>
       </c>
       <c r="C512" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D512" t="b">
         <v>1</v>
@@ -9451,7 +9371,7 @@
         <v>2010</v>
       </c>
       <c r="C513" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D513" t="b">
         <v>1</v>
@@ -9465,16 +9385,16 @@
         <v>50</v>
       </c>
       <c r="B514">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C514" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D514" t="b">
         <v>1</v>
       </c>
       <c r="E514" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.2">
@@ -9482,16 +9402,16 @@
         <v>50</v>
       </c>
       <c r="B515">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C515" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D515" t="b">
         <v>1</v>
       </c>
       <c r="E515" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.2">
@@ -9502,7 +9422,7 @@
         <v>2012</v>
       </c>
       <c r="C516" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D516" t="b">
         <v>1</v>
@@ -9519,7 +9439,7 @@
         <v>2012</v>
       </c>
       <c r="C517" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D517" t="b">
         <v>1</v>
@@ -9536,13 +9456,13 @@
         <v>2012</v>
       </c>
       <c r="C518" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D518" t="b">
         <v>1</v>
       </c>
       <c r="E518" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.2">
@@ -9553,13 +9473,13 @@
         <v>2012</v>
       </c>
       <c r="C519" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D519" t="b">
         <v>1</v>
       </c>
       <c r="E519" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.2">
@@ -9570,7 +9490,7 @@
         <v>2012</v>
       </c>
       <c r="C520" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D520" t="b">
         <v>1</v>
@@ -9587,7 +9507,7 @@
         <v>2012</v>
       </c>
       <c r="C521" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D521" t="b">
         <v>1</v>
@@ -9601,16 +9521,16 @@
         <v>50</v>
       </c>
       <c r="B522">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C522" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D522" t="b">
         <v>1</v>
       </c>
       <c r="E522" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.2">
@@ -9618,16 +9538,16 @@
         <v>50</v>
       </c>
       <c r="B523">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C523" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D523" t="b">
         <v>1</v>
       </c>
       <c r="E523" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.2">
@@ -9638,7 +9558,7 @@
         <v>2014</v>
       </c>
       <c r="C524" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D524" t="b">
         <v>1</v>
@@ -9655,7 +9575,7 @@
         <v>2014</v>
       </c>
       <c r="C525" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D525" t="b">
         <v>1</v>
@@ -9672,13 +9592,13 @@
         <v>2014</v>
       </c>
       <c r="C526" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D526" t="b">
         <v>1</v>
       </c>
       <c r="E526" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.2">
@@ -9689,13 +9609,13 @@
         <v>2014</v>
       </c>
       <c r="C527" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D527" t="b">
         <v>1</v>
       </c>
       <c r="E527" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.2">
@@ -9706,7 +9626,7 @@
         <v>2014</v>
       </c>
       <c r="C528" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D528" t="b">
         <v>1</v>
@@ -9723,7 +9643,7 @@
         <v>2014</v>
       </c>
       <c r="C529" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D529" t="b">
         <v>1</v>
@@ -9737,16 +9657,16 @@
         <v>50</v>
       </c>
       <c r="B530">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C530" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D530" t="b">
         <v>1</v>
       </c>
       <c r="E530" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.2">
@@ -9754,16 +9674,16 @@
         <v>50</v>
       </c>
       <c r="B531">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C531" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D531" t="b">
         <v>1</v>
       </c>
       <c r="E531" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
@@ -9774,7 +9694,7 @@
         <v>2016</v>
       </c>
       <c r="C532" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D532" t="b">
         <v>1</v>
@@ -9791,7 +9711,7 @@
         <v>2016</v>
       </c>
       <c r="C533" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D533" t="b">
         <v>1</v>
@@ -9808,13 +9728,13 @@
         <v>2016</v>
       </c>
       <c r="C534" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D534" t="b">
         <v>1</v>
       </c>
       <c r="E534" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.2">
@@ -9825,13 +9745,13 @@
         <v>2016</v>
       </c>
       <c r="C535" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D535" t="b">
         <v>1</v>
       </c>
       <c r="E535" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.2">
@@ -9842,7 +9762,7 @@
         <v>2016</v>
       </c>
       <c r="C536" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D536" t="b">
         <v>1</v>
@@ -9859,7 +9779,7 @@
         <v>2016</v>
       </c>
       <c r="C537" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D537" t="b">
         <v>1</v>
@@ -9870,10 +9790,10 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B538">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C538" t="s">
         <v>8</v>
@@ -9887,10 +9807,10 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B539">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C539" t="s">
         <v>27</v>
@@ -9907,10 +9827,10 @@
         <v>51</v>
       </c>
       <c r="B540">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C540" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D540" t="b">
         <v>1</v>
@@ -9924,10 +9844,10 @@
         <v>51</v>
       </c>
       <c r="B541">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C541" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D541" t="b">
         <v>1</v>
@@ -9944,7 +9864,7 @@
         <v>2012</v>
       </c>
       <c r="C542" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D542" t="b">
         <v>1</v>
@@ -9961,7 +9881,7 @@
         <v>2012</v>
       </c>
       <c r="C543" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D543" t="b">
         <v>1</v>
@@ -9975,10 +9895,10 @@
         <v>51</v>
       </c>
       <c r="B544">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C544" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D544" t="b">
         <v>1</v>
@@ -9992,10 +9912,10 @@
         <v>51</v>
       </c>
       <c r="B545">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C545" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D545" t="b">
         <v>1</v>
@@ -10009,10 +9929,10 @@
         <v>51</v>
       </c>
       <c r="B546">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C546" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D546" t="b">
         <v>1</v>
@@ -10026,10 +9946,10 @@
         <v>51</v>
       </c>
       <c r="B547">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C547" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D547" t="b">
         <v>1</v>
@@ -10043,10 +9963,10 @@
         <v>51</v>
       </c>
       <c r="B548">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C548" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D548" t="b">
         <v>1</v>
@@ -10060,10 +9980,10 @@
         <v>51</v>
       </c>
       <c r="B549">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C549" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D549" t="b">
         <v>1</v>
@@ -10077,7 +9997,7 @@
         <v>51</v>
       </c>
       <c r="B550">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -10094,7 +10014,7 @@
         <v>51</v>
       </c>
       <c r="B551">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C551" t="s">
         <v>27</v>
@@ -10108,36 +10028,36 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B552">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C552" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D552" t="b">
         <v>1</v>
       </c>
       <c r="E552" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B553">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C553" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D553" t="b">
         <v>1</v>
       </c>
       <c r="E553" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.2">
@@ -10145,7 +10065,7 @@
         <v>52</v>
       </c>
       <c r="B554">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C554" t="s">
         <v>10</v>
@@ -10162,7 +10082,7 @@
         <v>52</v>
       </c>
       <c r="B555">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C555" t="s">
         <v>13</v>
@@ -10179,16 +10099,16 @@
         <v>52</v>
       </c>
       <c r="B556">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C556" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D556" t="b">
         <v>1</v>
       </c>
       <c r="E556" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.2">
@@ -10196,16 +10116,16 @@
         <v>52</v>
       </c>
       <c r="B557">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C557" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D557" t="b">
         <v>1</v>
       </c>
       <c r="E557" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.2">
@@ -10216,13 +10136,13 @@
         <v>2012</v>
       </c>
       <c r="C558" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D558" t="b">
         <v>1</v>
       </c>
       <c r="E558" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.2">
@@ -10233,13 +10153,13 @@
         <v>2012</v>
       </c>
       <c r="C559" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D559" t="b">
         <v>1</v>
       </c>
       <c r="E559" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.2">
@@ -10247,7 +10167,7 @@
         <v>52</v>
       </c>
       <c r="B560">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C560" t="s">
         <v>10</v>
@@ -10264,7 +10184,7 @@
         <v>52</v>
       </c>
       <c r="B561">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C561" t="s">
         <v>13</v>
@@ -10281,16 +10201,16 @@
         <v>52</v>
       </c>
       <c r="B562">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C562" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D562" t="b">
         <v>1</v>
       </c>
       <c r="E562" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.2">
@@ -10298,16 +10218,16 @@
         <v>52</v>
       </c>
       <c r="B563">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C563" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D563" t="b">
         <v>1</v>
       </c>
       <c r="E563" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.2">
@@ -10318,13 +10238,13 @@
         <v>2016</v>
       </c>
       <c r="C564" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D564" t="b">
         <v>1</v>
       </c>
       <c r="E564" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
@@ -10335,13 +10255,13 @@
         <v>2016</v>
       </c>
       <c r="C565" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D565" t="b">
         <v>1</v>
       </c>
       <c r="E565" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.2">
@@ -10349,7 +10269,7 @@
         <v>52</v>
       </c>
       <c r="B566">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C566" t="s">
         <v>10</v>
@@ -10366,7 +10286,7 @@
         <v>52</v>
       </c>
       <c r="B567">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C567" t="s">
         <v>13</v>
@@ -10380,36 +10300,36 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B568">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C568" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D568" t="b">
         <v>1</v>
       </c>
       <c r="E568" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B569">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C569" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D569" t="b">
         <v>1</v>
       </c>
       <c r="E569" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.2">
@@ -10420,7 +10340,7 @@
         <v>2010</v>
       </c>
       <c r="C570" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D570" t="b">
         <v>1</v>
@@ -10437,7 +10357,7 @@
         <v>2010</v>
       </c>
       <c r="C571" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D571" t="b">
         <v>1</v>
@@ -10451,10 +10371,10 @@
         <v>53</v>
       </c>
       <c r="B572">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C572" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D572" t="b">
         <v>1</v>
@@ -10468,10 +10388,10 @@
         <v>53</v>
       </c>
       <c r="B573">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C573" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D573" t="b">
         <v>1</v>
@@ -10485,10 +10405,10 @@
         <v>53</v>
       </c>
       <c r="B574">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C574" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D574" t="b">
         <v>1</v>
@@ -10502,10 +10422,10 @@
         <v>53</v>
       </c>
       <c r="B575">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C575" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D575" t="b">
         <v>1</v>
@@ -10522,7 +10442,7 @@
         <v>2014</v>
       </c>
       <c r="C576" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D576" t="b">
         <v>1</v>
@@ -10539,7 +10459,7 @@
         <v>2014</v>
       </c>
       <c r="C577" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D577" t="b">
         <v>1</v>
@@ -10550,13 +10470,13 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B578">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C578" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D578" t="b">
         <v>1</v>
@@ -10567,13 +10487,13 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B579">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C579" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D579" t="b">
         <v>1</v>
@@ -10590,7 +10510,7 @@
         <v>2012</v>
       </c>
       <c r="C580" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D580" t="b">
         <v>1</v>
@@ -10607,7 +10527,7 @@
         <v>2012</v>
       </c>
       <c r="C581" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D581" t="b">
         <v>1</v>
@@ -10621,10 +10541,10 @@
         <v>54</v>
       </c>
       <c r="B582">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C582" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D582" t="b">
         <v>1</v>
@@ -10638,10 +10558,10 @@
         <v>54</v>
       </c>
       <c r="B583">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C583" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D583" t="b">
         <v>1</v>
@@ -10658,7 +10578,7 @@
         <v>2016</v>
       </c>
       <c r="C584" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D584" t="b">
         <v>1</v>
@@ -10675,7 +10595,7 @@
         <v>2016</v>
       </c>
       <c r="C585" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D585" t="b">
         <v>1</v>
@@ -10686,13 +10606,13 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B586">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C586" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D586" t="b">
         <v>1</v>
@@ -10703,13 +10623,13 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B587">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C587" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D587" t="b">
         <v>1</v>
@@ -10726,7 +10646,7 @@
         <v>2012</v>
       </c>
       <c r="C588" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D588" t="b">
         <v>1</v>
@@ -10743,7 +10663,7 @@
         <v>2012</v>
       </c>
       <c r="C589" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D589" t="b">
         <v>1</v>
@@ -10757,10 +10677,10 @@
         <v>55</v>
       </c>
       <c r="B590">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C590" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D590" t="b">
         <v>1</v>
@@ -10774,10 +10694,10 @@
         <v>55</v>
       </c>
       <c r="B591">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C591" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D591" t="b">
         <v>1</v>
@@ -10794,7 +10714,7 @@
         <v>2016</v>
       </c>
       <c r="C592" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D592" t="b">
         <v>1</v>
@@ -10811,7 +10731,7 @@
         <v>2016</v>
       </c>
       <c r="C593" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D593" t="b">
         <v>1</v>
@@ -10822,10 +10742,10 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B594">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C594" t="s">
         <v>10</v>
@@ -10834,15 +10754,15 @@
         <v>1</v>
       </c>
       <c r="E594" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B595">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C595" t="s">
         <v>13</v>
@@ -10851,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="E595" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.2">
@@ -10859,16 +10779,16 @@
         <v>56</v>
       </c>
       <c r="B596">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C596" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D596" t="b">
         <v>1</v>
       </c>
       <c r="E596" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.2">
@@ -10876,16 +10796,16 @@
         <v>56</v>
       </c>
       <c r="B597">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C597" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D597" t="b">
         <v>1</v>
       </c>
       <c r="E597" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.2">
@@ -10893,16 +10813,16 @@
         <v>56</v>
       </c>
       <c r="B598">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C598" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D598" t="b">
         <v>1</v>
       </c>
       <c r="E598" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.2">
@@ -10910,16 +10830,16 @@
         <v>56</v>
       </c>
       <c r="B599">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C599" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D599" t="b">
         <v>1</v>
       </c>
       <c r="E599" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.2">
@@ -10927,16 +10847,16 @@
         <v>56</v>
       </c>
       <c r="B600">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C600" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D600" t="b">
         <v>1</v>
       </c>
       <c r="E600" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.2">
@@ -10944,16 +10864,16 @@
         <v>56</v>
       </c>
       <c r="B601">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C601" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D601" t="b">
         <v>1</v>
       </c>
       <c r="E601" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.2">
@@ -10964,7 +10884,7 @@
         <v>2012</v>
       </c>
       <c r="C602" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D602" t="b">
         <v>1</v>
@@ -10981,7 +10901,7 @@
         <v>2012</v>
       </c>
       <c r="C603" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D603" t="b">
         <v>1</v>
@@ -10995,16 +10915,16 @@
         <v>56</v>
       </c>
       <c r="B604">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C604" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D604" t="b">
         <v>1</v>
       </c>
       <c r="E604" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.2">
@@ -11012,16 +10932,16 @@
         <v>56</v>
       </c>
       <c r="B605">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C605" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D605" t="b">
         <v>1</v>
       </c>
       <c r="E605" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.2">
@@ -11032,13 +10952,13 @@
         <v>2014</v>
       </c>
       <c r="C606" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D606" t="b">
         <v>1</v>
       </c>
       <c r="E606" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.2">
@@ -11049,13 +10969,13 @@
         <v>2014</v>
       </c>
       <c r="C607" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D607" t="b">
         <v>1</v>
       </c>
       <c r="E607" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.2">
@@ -11063,16 +10983,16 @@
         <v>56</v>
       </c>
       <c r="B608">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C608" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D608" t="b">
         <v>1</v>
       </c>
       <c r="E608" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.2">
@@ -11080,16 +11000,16 @@
         <v>56</v>
       </c>
       <c r="B609">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C609" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D609" t="b">
         <v>1</v>
       </c>
       <c r="E609" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.2">
@@ -11100,7 +11020,7 @@
         <v>2016</v>
       </c>
       <c r="C610" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D610" t="b">
         <v>1</v>
@@ -11117,7 +11037,7 @@
         <v>2016</v>
       </c>
       <c r="C611" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D611" t="b">
         <v>1</v>
@@ -11128,13 +11048,13 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B612">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C612" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D612" t="b">
         <v>1</v>
@@ -11145,13 +11065,13 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B613">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C613" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D613" t="b">
         <v>1</v>
@@ -11168,7 +11088,7 @@
         <v>2006</v>
       </c>
       <c r="C614" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D614" t="b">
         <v>1</v>
@@ -11185,7 +11105,7 @@
         <v>2006</v>
       </c>
       <c r="C615" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D615" t="b">
         <v>1</v>
@@ -11199,10 +11119,10 @@
         <v>58</v>
       </c>
       <c r="B616">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C616" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D616" t="b">
         <v>1</v>
@@ -11216,10 +11136,10 @@
         <v>58</v>
       </c>
       <c r="B617">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C617" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D617" t="b">
         <v>1</v>
@@ -11236,7 +11156,7 @@
         <v>2010</v>
       </c>
       <c r="C618" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D618" t="b">
         <v>1</v>
@@ -11253,7 +11173,7 @@
         <v>2010</v>
       </c>
       <c r="C619" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D619" t="b">
         <v>1</v>
@@ -11267,10 +11187,10 @@
         <v>58</v>
       </c>
       <c r="B620">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C620" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D620" t="b">
         <v>1</v>
@@ -11284,10 +11204,10 @@
         <v>58</v>
       </c>
       <c r="B621">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C621" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D621" t="b">
         <v>1</v>
@@ -11304,7 +11224,7 @@
         <v>2014</v>
       </c>
       <c r="C622" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D622" t="b">
         <v>1</v>
@@ -11321,7 +11241,7 @@
         <v>2014</v>
       </c>
       <c r="C623" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D623" t="b">
         <v>1</v>
@@ -11332,13 +11252,13 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B624">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C624" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D624" t="b">
         <v>1</v>
@@ -11349,13 +11269,13 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B625">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C625" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D625" t="b">
         <v>1</v>
@@ -11372,13 +11292,13 @@
         <v>2006</v>
       </c>
       <c r="C626" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D626" t="b">
         <v>1</v>
       </c>
       <c r="E626" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.2">
@@ -11389,13 +11309,13 @@
         <v>2006</v>
       </c>
       <c r="C627" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D627" t="b">
         <v>1</v>
       </c>
       <c r="E627" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.2">
@@ -11403,16 +11323,16 @@
         <v>59</v>
       </c>
       <c r="B628">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C628" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D628" t="b">
         <v>1</v>
       </c>
       <c r="E628" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.2">
@@ -11420,16 +11340,16 @@
         <v>59</v>
       </c>
       <c r="B629">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C629" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D629" t="b">
         <v>1</v>
       </c>
       <c r="E629" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.2">
@@ -11440,13 +11360,13 @@
         <v>2010</v>
       </c>
       <c r="C630" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D630" t="b">
         <v>1</v>
       </c>
       <c r="E630" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.2">
@@ -11457,13 +11377,13 @@
         <v>2010</v>
       </c>
       <c r="C631" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D631" t="b">
         <v>1</v>
       </c>
       <c r="E631" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.2">
@@ -11471,7 +11391,7 @@
         <v>59</v>
       </c>
       <c r="B632">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C632" t="s">
         <v>10</v>
@@ -11488,7 +11408,7 @@
         <v>59</v>
       </c>
       <c r="B633">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C633" t="s">
         <v>13</v>
@@ -11505,16 +11425,16 @@
         <v>59</v>
       </c>
       <c r="B634">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C634" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D634" t="b">
         <v>1</v>
       </c>
       <c r="E634" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.2">
@@ -11522,16 +11442,16 @@
         <v>59</v>
       </c>
       <c r="B635">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C635" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D635" t="b">
         <v>1</v>
       </c>
       <c r="E635" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.2">
@@ -11542,13 +11462,13 @@
         <v>2014</v>
       </c>
       <c r="C636" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D636" t="b">
         <v>1</v>
       </c>
       <c r="E636" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.2">
@@ -11559,13 +11479,13 @@
         <v>2014</v>
       </c>
       <c r="C637" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D637" t="b">
         <v>1</v>
       </c>
       <c r="E637" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.2">
@@ -11573,7 +11493,7 @@
         <v>59</v>
       </c>
       <c r="B638">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C638" t="s">
         <v>10</v>
@@ -11590,7 +11510,7 @@
         <v>59</v>
       </c>
       <c r="B639">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C639" t="s">
         <v>13</v>
@@ -11604,36 +11524,36 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B640">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C640" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D640" t="b">
         <v>1</v>
       </c>
       <c r="E640" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B641">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C641" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D641" t="b">
         <v>1</v>
       </c>
       <c r="E641" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.2">
@@ -11644,7 +11564,7 @@
         <v>2012</v>
       </c>
       <c r="C642" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D642" t="b">
         <v>1</v>
@@ -11661,7 +11581,7 @@
         <v>2012</v>
       </c>
       <c r="C643" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D643" t="b">
         <v>1</v>
@@ -11675,10 +11595,10 @@
         <v>60</v>
       </c>
       <c r="B644">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C644" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D644" t="b">
         <v>1</v>
@@ -11692,10 +11612,10 @@
         <v>60</v>
       </c>
       <c r="B645">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C645" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D645" t="b">
         <v>1</v>
@@ -11712,7 +11632,7 @@
         <v>2016</v>
       </c>
       <c r="C646" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D646" t="b">
         <v>1</v>
@@ -11729,7 +11649,7 @@
         <v>2016</v>
       </c>
       <c r="C647" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D647" t="b">
         <v>1</v>
@@ -11740,13 +11660,13 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B648">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C648" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D648" t="b">
         <v>1</v>
@@ -11757,13 +11677,13 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B649">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C649" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D649" t="b">
         <v>1</v>
@@ -11777,7 +11697,7 @@
         <v>61</v>
       </c>
       <c r="B650">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C650" t="s">
         <v>8</v>
@@ -11794,7 +11714,7 @@
         <v>61</v>
       </c>
       <c r="B651">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C651" t="s">
         <v>27</v>
@@ -11811,10 +11731,10 @@
         <v>61</v>
       </c>
       <c r="B652">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C652" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D652" t="b">
         <v>1</v>
@@ -11828,10 +11748,10 @@
         <v>61</v>
       </c>
       <c r="B653">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C653" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D653" t="b">
         <v>1</v>
@@ -11848,7 +11768,7 @@
         <v>2012</v>
       </c>
       <c r="C654" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D654" t="b">
         <v>1</v>
@@ -11865,7 +11785,7 @@
         <v>2012</v>
       </c>
       <c r="C655" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D655" t="b">
         <v>1</v>
@@ -11879,10 +11799,10 @@
         <v>61</v>
       </c>
       <c r="B656">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C656" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D656" t="b">
         <v>1</v>
@@ -11896,10 +11816,10 @@
         <v>61</v>
       </c>
       <c r="B657">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C657" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D657" t="b">
         <v>1</v>
@@ -11916,7 +11836,7 @@
         <v>2016</v>
       </c>
       <c r="C658" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D658" t="b">
         <v>1</v>
@@ -11933,7 +11853,7 @@
         <v>2016</v>
       </c>
       <c r="C659" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D659" t="b">
         <v>1</v>
@@ -11944,13 +11864,13 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B660">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C660" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D660" t="b">
         <v>1</v>
@@ -11961,13 +11881,13 @@
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B661">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C661" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D661" t="b">
         <v>1</v>
@@ -11984,7 +11904,7 @@
         <v>2012</v>
       </c>
       <c r="C662" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D662" t="b">
         <v>1</v>
@@ -12001,7 +11921,7 @@
         <v>2012</v>
       </c>
       <c r="C663" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D663" t="b">
         <v>1</v>
@@ -12015,10 +11935,10 @@
         <v>62</v>
       </c>
       <c r="B664">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C664" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D664" t="b">
         <v>1</v>
@@ -12032,10 +11952,10 @@
         <v>62</v>
       </c>
       <c r="B665">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C665" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D665" t="b">
         <v>1</v>
@@ -12052,7 +11972,7 @@
         <v>2016</v>
       </c>
       <c r="C666" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D666" t="b">
         <v>1</v>
@@ -12069,7 +11989,7 @@
         <v>2016</v>
       </c>
       <c r="C667" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D667" t="b">
         <v>1</v>
@@ -12080,36 +12000,36 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B668">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C668" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D668" t="b">
         <v>1</v>
       </c>
       <c r="E668" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B669">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C669" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D669" t="b">
         <v>1</v>
       </c>
       <c r="E669" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.2">
@@ -12120,7 +12040,7 @@
         <v>2006</v>
       </c>
       <c r="C670" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D670" t="b">
         <v>1</v>
@@ -12137,7 +12057,7 @@
         <v>2006</v>
       </c>
       <c r="C671" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D671" t="b">
         <v>1</v>
@@ -12151,10 +12071,10 @@
         <v>63</v>
       </c>
       <c r="B672">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C672" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D672" t="b">
         <v>1</v>
@@ -12168,10 +12088,10 @@
         <v>63</v>
       </c>
       <c r="B673">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C673" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D673" t="b">
         <v>1</v>
@@ -12188,7 +12108,7 @@
         <v>2010</v>
       </c>
       <c r="C674" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D674" t="b">
         <v>1</v>
@@ -12205,7 +12125,7 @@
         <v>2010</v>
       </c>
       <c r="C675" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D675" t="b">
         <v>1</v>
@@ -12219,10 +12139,10 @@
         <v>63</v>
       </c>
       <c r="B676">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C676" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D676" t="b">
         <v>1</v>
@@ -12236,10 +12156,10 @@
         <v>63</v>
       </c>
       <c r="B677">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C677" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D677" t="b">
         <v>1</v>
@@ -12256,7 +12176,7 @@
         <v>2012</v>
       </c>
       <c r="C678" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D678" t="b">
         <v>1</v>
@@ -12273,7 +12193,7 @@
         <v>2012</v>
       </c>
       <c r="C679" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D679" t="b">
         <v>1</v>
@@ -12287,10 +12207,10 @@
         <v>63</v>
       </c>
       <c r="B680">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C680" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D680" t="b">
         <v>1</v>
@@ -12304,10 +12224,10 @@
         <v>63</v>
       </c>
       <c r="B681">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C681" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D681" t="b">
         <v>1</v>
@@ -12324,7 +12244,7 @@
         <v>2014</v>
       </c>
       <c r="C682" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D682" t="b">
         <v>1</v>
@@ -12341,7 +12261,7 @@
         <v>2014</v>
       </c>
       <c r="C683" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D683" t="b">
         <v>1</v>
@@ -12355,10 +12275,10 @@
         <v>63</v>
       </c>
       <c r="B684">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C684" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D684" t="b">
         <v>1</v>
@@ -12372,10 +12292,10 @@
         <v>63</v>
       </c>
       <c r="B685">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C685" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D685" t="b">
         <v>1</v>
@@ -12392,7 +12312,7 @@
         <v>2016</v>
       </c>
       <c r="C686" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D686" t="b">
         <v>1</v>
@@ -12409,7 +12329,7 @@
         <v>2016</v>
       </c>
       <c r="C687" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D687" t="b">
         <v>1</v>
@@ -12420,10 +12340,10 @@
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B688">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C688" t="s">
         <v>10</v>
@@ -12437,10 +12357,10 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B689">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C689" t="s">
         <v>13</v>
@@ -12457,7 +12377,7 @@
         <v>64</v>
       </c>
       <c r="B690">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C690" t="s">
         <v>10</v>
@@ -12474,7 +12394,7 @@
         <v>64</v>
       </c>
       <c r="B691">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C691" t="s">
         <v>13</v>
@@ -12491,16 +12411,16 @@
         <v>64</v>
       </c>
       <c r="B692">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C692" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D692" t="b">
         <v>1</v>
       </c>
       <c r="E692" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.2">
@@ -12508,16 +12428,16 @@
         <v>64</v>
       </c>
       <c r="B693">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C693" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D693" t="b">
         <v>1</v>
       </c>
       <c r="E693" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.2">
@@ -12528,7 +12448,7 @@
         <v>2012</v>
       </c>
       <c r="C694" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D694" t="b">
         <v>1</v>
@@ -12545,7 +12465,7 @@
         <v>2012</v>
       </c>
       <c r="C695" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D695" t="b">
         <v>1</v>
@@ -12559,7 +12479,7 @@
         <v>64</v>
       </c>
       <c r="B696">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C696" t="s">
         <v>10</v>
@@ -12568,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="E696" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.2">
@@ -12576,7 +12496,7 @@
         <v>64</v>
       </c>
       <c r="B697">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C697" t="s">
         <v>13</v>
@@ -12585,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="E697" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.2">
@@ -12593,16 +12513,16 @@
         <v>64</v>
       </c>
       <c r="B698">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C698" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D698" t="b">
         <v>1</v>
       </c>
       <c r="E698" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.2">
@@ -12610,16 +12530,16 @@
         <v>64</v>
       </c>
       <c r="B699">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C699" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D699" t="b">
         <v>1</v>
       </c>
       <c r="E699" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.2">
@@ -12630,7 +12550,7 @@
         <v>2016</v>
       </c>
       <c r="C700" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D700" t="b">
         <v>1</v>
@@ -12647,7 +12567,7 @@
         <v>2016</v>
       </c>
       <c r="C701" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D701" t="b">
         <v>1</v>
@@ -12658,13 +12578,13 @@
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B702">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C702" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D702" t="b">
         <v>1</v>
@@ -12675,13 +12595,13 @@
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B703">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C703" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D703" t="b">
         <v>1</v>
@@ -12698,13 +12618,13 @@
         <v>2010</v>
       </c>
       <c r="C704" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D704" t="b">
         <v>1</v>
       </c>
       <c r="E704" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.2">
@@ -12715,13 +12635,13 @@
         <v>2010</v>
       </c>
       <c r="C705" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D705" t="b">
         <v>1</v>
       </c>
       <c r="E705" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.2">
@@ -12729,7 +12649,7 @@
         <v>65</v>
       </c>
       <c r="B706">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C706" t="s">
         <v>10</v>
@@ -12746,7 +12666,7 @@
         <v>65</v>
       </c>
       <c r="B707">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C707" t="s">
         <v>13</v>
@@ -12763,7 +12683,7 @@
         <v>65</v>
       </c>
       <c r="B708">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C708" t="s">
         <v>10</v>
@@ -12780,7 +12700,7 @@
         <v>65</v>
       </c>
       <c r="B709">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C709" t="s">
         <v>13</v>
@@ -12797,7 +12717,7 @@
         <v>65</v>
       </c>
       <c r="B710">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C710" t="s">
         <v>10</v>
@@ -12814,7 +12734,7 @@
         <v>65</v>
       </c>
       <c r="B711">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C711" t="s">
         <v>13</v>
@@ -12831,7 +12751,7 @@
         <v>65</v>
       </c>
       <c r="B712">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C712" t="s">
         <v>10</v>
@@ -12848,7 +12768,7 @@
         <v>65</v>
       </c>
       <c r="B713">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C713" t="s">
         <v>13</v>
@@ -12865,7 +12785,7 @@
         <v>65</v>
       </c>
       <c r="B714">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C714" t="s">
         <v>10</v>
@@ -12882,7 +12802,7 @@
         <v>65</v>
       </c>
       <c r="B715">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C715" t="s">
         <v>13</v>
@@ -12899,7 +12819,7 @@
         <v>65</v>
       </c>
       <c r="B716">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C716" t="s">
         <v>10</v>
@@ -12916,7 +12836,7 @@
         <v>65</v>
       </c>
       <c r="B717">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C717" t="s">
         <v>13</v>
@@ -12930,36 +12850,36 @@
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B718">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C718" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D718" t="b">
         <v>1</v>
       </c>
       <c r="E718" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B719">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C719" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D719" t="b">
         <v>1</v>
       </c>
       <c r="E719" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.2">
@@ -12970,7 +12890,7 @@
         <v>2008</v>
       </c>
       <c r="C720" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D720" t="b">
         <v>1</v>
@@ -12987,7 +12907,7 @@
         <v>2008</v>
       </c>
       <c r="C721" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D721" t="b">
         <v>1</v>
@@ -13001,10 +12921,10 @@
         <v>66</v>
       </c>
       <c r="B722">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C722" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D722" t="b">
         <v>1</v>
@@ -13018,10 +12938,10 @@
         <v>66</v>
       </c>
       <c r="B723">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C723" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D723" t="b">
         <v>1</v>
@@ -13038,7 +12958,7 @@
         <v>2010</v>
       </c>
       <c r="C724" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D724" t="b">
         <v>1</v>
@@ -13055,7 +12975,7 @@
         <v>2010</v>
       </c>
       <c r="C725" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D725" t="b">
         <v>1</v>
@@ -13072,7 +12992,7 @@
         <v>2010</v>
       </c>
       <c r="C726" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D726" t="b">
         <v>1</v>
@@ -13089,7 +13009,7 @@
         <v>2010</v>
       </c>
       <c r="C727" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D727" t="b">
         <v>1</v>
@@ -13106,7 +13026,7 @@
         <v>2010</v>
       </c>
       <c r="C728" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D728" t="b">
         <v>1</v>
@@ -13123,7 +13043,7 @@
         <v>2010</v>
       </c>
       <c r="C729" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D729" t="b">
         <v>1</v>
@@ -13137,10 +13057,10 @@
         <v>66</v>
       </c>
       <c r="B730">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C730" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D730" t="b">
         <v>1</v>
@@ -13154,10 +13074,10 @@
         <v>66</v>
       </c>
       <c r="B731">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C731" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D731" t="b">
         <v>1</v>
@@ -13174,7 +13094,7 @@
         <v>2012</v>
       </c>
       <c r="C732" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D732" t="b">
         <v>1</v>
@@ -13191,7 +13111,7 @@
         <v>2012</v>
       </c>
       <c r="C733" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D733" t="b">
         <v>1</v>
@@ -13208,7 +13128,7 @@
         <v>2012</v>
       </c>
       <c r="C734" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D734" t="b">
         <v>1</v>
@@ -13225,7 +13145,7 @@
         <v>2012</v>
       </c>
       <c r="C735" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D735" t="b">
         <v>1</v>
@@ -13242,7 +13162,7 @@
         <v>2012</v>
       </c>
       <c r="C736" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D736" t="b">
         <v>1</v>
@@ -13259,7 +13179,7 @@
         <v>2012</v>
       </c>
       <c r="C737" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D737" t="b">
         <v>1</v>
@@ -13273,10 +13193,10 @@
         <v>66</v>
       </c>
       <c r="B738">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C738" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D738" t="b">
         <v>1</v>
@@ -13290,10 +13210,10 @@
         <v>66</v>
       </c>
       <c r="B739">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C739" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D739" t="b">
         <v>1</v>
@@ -13310,7 +13230,7 @@
         <v>2014</v>
       </c>
       <c r="C740" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D740" t="b">
         <v>1</v>
@@ -13327,7 +13247,7 @@
         <v>2014</v>
       </c>
       <c r="C741" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D741" t="b">
         <v>1</v>
@@ -13344,7 +13264,7 @@
         <v>2014</v>
       </c>
       <c r="C742" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D742" t="b">
         <v>1</v>
@@ -13361,7 +13281,7 @@
         <v>2014</v>
       </c>
       <c r="C743" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D743" t="b">
         <v>1</v>
@@ -13378,7 +13298,7 @@
         <v>2014</v>
       </c>
       <c r="C744" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D744" t="b">
         <v>1</v>
@@ -13395,7 +13315,7 @@
         <v>2014</v>
       </c>
       <c r="C745" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D745" t="b">
         <v>1</v>
@@ -13409,10 +13329,10 @@
         <v>66</v>
       </c>
       <c r="B746">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C746" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D746" t="b">
         <v>1</v>
@@ -13426,10 +13346,10 @@
         <v>66</v>
       </c>
       <c r="B747">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C747" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D747" t="b">
         <v>1</v>
@@ -13446,7 +13366,7 @@
         <v>2016</v>
       </c>
       <c r="C748" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D748" t="b">
         <v>1</v>
@@ -13463,7 +13383,7 @@
         <v>2016</v>
       </c>
       <c r="C749" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D749" t="b">
         <v>1</v>
@@ -13480,7 +13400,7 @@
         <v>2016</v>
       </c>
       <c r="C750" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D750" t="b">
         <v>1</v>
@@ -13497,7 +13417,7 @@
         <v>2016</v>
       </c>
       <c r="C751" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D751" t="b">
         <v>1</v>
@@ -13514,7 +13434,7 @@
         <v>2016</v>
       </c>
       <c r="C752" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D752" t="b">
         <v>1</v>
@@ -13531,7 +13451,7 @@
         <v>2016</v>
       </c>
       <c r="C753" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D753" t="b">
         <v>1</v>
@@ -13548,7 +13468,7 @@
         <v>2016</v>
       </c>
       <c r="C754" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D754" t="b">
         <v>1</v>
@@ -13565,7 +13485,7 @@
         <v>2016</v>
       </c>
       <c r="C755" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D755" t="b">
         <v>1</v>
@@ -13579,7 +13499,7 @@
         <v>66</v>
       </c>
       <c r="B756">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C756" t="s">
         <v>8</v>
@@ -13596,7 +13516,7 @@
         <v>66</v>
       </c>
       <c r="B757">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C757" t="s">
         <v>27</v>
@@ -13613,7 +13533,7 @@
         <v>66</v>
       </c>
       <c r="B758">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C758" t="s">
         <v>8</v>
@@ -13630,7 +13550,7 @@
         <v>66</v>
       </c>
       <c r="B759">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C759" t="s">
         <v>27</v>
@@ -13647,7 +13567,7 @@
         <v>66</v>
       </c>
       <c r="B760">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C760" t="s">
         <v>8</v>
@@ -13664,7 +13584,7 @@
         <v>66</v>
       </c>
       <c r="B761">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C761" t="s">
         <v>27</v>
@@ -13678,13 +13598,13 @@
     </row>
     <row r="762" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B762">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C762" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D762" t="b">
         <v>1</v>
@@ -13695,13 +13615,13 @@
     </row>
     <row r="763" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B763">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C763" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D763" t="b">
         <v>1</v>
@@ -13718,7 +13638,7 @@
         <v>2010</v>
       </c>
       <c r="C764" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D764" t="b">
         <v>1</v>
@@ -13735,7 +13655,7 @@
         <v>2010</v>
       </c>
       <c r="C765" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D765" t="b">
         <v>1</v>
@@ -13749,10 +13669,10 @@
         <v>67</v>
       </c>
       <c r="B766">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C766" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D766" t="b">
         <v>1</v>
@@ -13766,10 +13686,10 @@
         <v>67</v>
       </c>
       <c r="B767">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C767" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D767" t="b">
         <v>1</v>
@@ -13786,7 +13706,7 @@
         <v>2014</v>
       </c>
       <c r="C768" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D768" t="b">
         <v>1</v>
@@ -13803,7 +13723,7 @@
         <v>2014</v>
       </c>
       <c r="C769" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D769" t="b">
         <v>1</v>
@@ -13817,10 +13737,10 @@
         <v>67</v>
       </c>
       <c r="B770">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C770" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D770" t="b">
         <v>1</v>
@@ -13834,10 +13754,10 @@
         <v>67</v>
       </c>
       <c r="B771">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C771" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D771" t="b">
         <v>1</v>
@@ -13848,10 +13768,10 @@
     </row>
     <row r="772" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B772">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C772" t="s">
         <v>9</v>
@@ -13865,10 +13785,10 @@
     </row>
     <row r="773" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B773">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C773" t="s">
         <v>14</v>
@@ -13888,7 +13808,7 @@
         <v>2010</v>
       </c>
       <c r="C774" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D774" t="b">
         <v>1</v>
@@ -13905,7 +13825,7 @@
         <v>2010</v>
       </c>
       <c r="C775" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D775" t="b">
         <v>1</v>
@@ -13919,10 +13839,10 @@
         <v>68</v>
       </c>
       <c r="B776">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C776" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D776" t="b">
         <v>1</v>
@@ -13936,10 +13856,10 @@
         <v>68</v>
       </c>
       <c r="B777">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C777" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D777" t="b">
         <v>1</v>
@@ -13956,7 +13876,7 @@
         <v>2014</v>
       </c>
       <c r="C778" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D778" t="b">
         <v>1</v>
@@ -13973,7 +13893,7 @@
         <v>2014</v>
       </c>
       <c r="C779" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D779" t="b">
         <v>1</v>
@@ -13984,13 +13904,13 @@
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B780">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C780" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D780" t="b">
         <v>1</v>
@@ -14001,13 +13921,13 @@
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B781">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C781" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D781" t="b">
         <v>1</v>
@@ -14024,7 +13944,7 @@
         <v>2012</v>
       </c>
       <c r="C782" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D782" t="b">
         <v>1</v>
@@ -14041,7 +13961,7 @@
         <v>2012</v>
       </c>
       <c r="C783" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D783" t="b">
         <v>1</v>
@@ -14055,10 +13975,10 @@
         <v>69</v>
       </c>
       <c r="B784">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C784" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D784" t="b">
         <v>1</v>
@@ -14072,10 +13992,10 @@
         <v>69</v>
       </c>
       <c r="B785">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C785" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D785" t="b">
         <v>1</v>
@@ -14092,7 +14012,7 @@
         <v>2016</v>
       </c>
       <c r="C786" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D786" t="b">
         <v>1</v>
@@ -14109,7 +14029,7 @@
         <v>2016</v>
       </c>
       <c r="C787" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D787" t="b">
         <v>1</v>
@@ -14120,36 +14040,36 @@
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B788">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C788" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D788" t="b">
         <v>1</v>
       </c>
       <c r="E788" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B789">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C789" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D789" t="b">
         <v>1</v>
       </c>
       <c r="E789" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.2">
@@ -14157,7 +14077,7 @@
         <v>70</v>
       </c>
       <c r="B790">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C790" t="s">
         <v>9</v>
@@ -14174,7 +14094,7 @@
         <v>70</v>
       </c>
       <c r="B791">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C791" t="s">
         <v>14</v>
@@ -14191,7 +14111,7 @@
         <v>70</v>
       </c>
       <c r="B792">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C792" t="s">
         <v>9</v>
@@ -14208,7 +14128,7 @@
         <v>70</v>
       </c>
       <c r="B793">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C793" t="s">
         <v>14</v>
@@ -14228,13 +14148,13 @@
         <v>2012</v>
       </c>
       <c r="C794" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D794" t="b">
         <v>1</v>
       </c>
       <c r="E794" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="795" spans="1:5" x14ac:dyDescent="0.2">
@@ -14245,13 +14165,13 @@
         <v>2012</v>
       </c>
       <c r="C795" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D795" t="b">
         <v>1</v>
       </c>
       <c r="E795" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.2">
@@ -14259,16 +14179,16 @@
         <v>70</v>
       </c>
       <c r="B796">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C796" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D796" t="b">
         <v>1</v>
       </c>
       <c r="E796" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.2">
@@ -14276,16 +14196,16 @@
         <v>70</v>
       </c>
       <c r="B797">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C797" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D797" t="b">
         <v>1</v>
       </c>
       <c r="E797" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.2">
@@ -14293,7 +14213,7 @@
         <v>70</v>
       </c>
       <c r="B798">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C798" t="s">
         <v>9</v>
@@ -14310,7 +14230,7 @@
         <v>70</v>
       </c>
       <c r="B799">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C799" t="s">
         <v>14</v>
@@ -14330,13 +14250,13 @@
         <v>2016</v>
       </c>
       <c r="C800" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D800" t="b">
         <v>1</v>
       </c>
       <c r="E800" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.2">
@@ -14347,21 +14267,21 @@
         <v>2016</v>
       </c>
       <c r="C801" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D801" t="b">
         <v>1</v>
       </c>
       <c r="E801" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B802">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C802" t="s">
         <v>10</v>
@@ -14370,94 +14290,80 @@
         <v>1</v>
       </c>
       <c r="E802" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
+        <v>70</v>
+      </c>
+      <c r="B803">
+        <v>2016</v>
+      </c>
+      <c r="C803" t="s">
+        <v>13</v>
+      </c>
+      <c r="D803" t="b">
+        <v>1</v>
+      </c>
+      <c r="E803" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A804" t="s">
         <v>54</v>
       </c>
-      <c r="B803">
+      <c r="B804">
         <v>2022</v>
       </c>
-      <c r="C803" t="s">
-        <v>13</v>
-      </c>
-      <c r="D803" t="b">
-        <v>1</v>
-      </c>
-      <c r="E803" t="s">
+      <c r="C804" t="s">
+        <v>10</v>
+      </c>
+      <c r="D804" t="b">
+        <v>1</v>
+      </c>
+      <c r="E804" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A805" t="s">
+        <v>54</v>
+      </c>
+      <c r="B805">
+        <v>2022</v>
+      </c>
+      <c r="C805" t="s">
+        <v>13</v>
+      </c>
+      <c r="D805" t="b">
+        <v>1</v>
+      </c>
+      <c r="E805" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="16" priority="17" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="4" priority="17" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:E61 A70:E1048576 D62:E69 A62:B69">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="CANDIDATE">
+  <conditionalFormatting sqref="A1:E1048576">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62:K70">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="1" priority="13" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",K62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",K62)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C62:C63">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C62)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C62)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C64">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C64)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C64)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C65">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C65)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C65)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C66:C67">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C66)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C66)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C68">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C68)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C68)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C69">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="CANDIDATE">
-      <formula>NOT(ISERROR(SEARCH("CANDIDATE",C69)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="PARTY">
-      <formula>NOT(ISERROR(SEARCH("PARTY",C69)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/misc./skip_conditions_final.xlsx
+++ b/data/misc./skip_conditions_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/misc./"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F36F64-DD12-7C44-9732-9E994F3FB7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652A9EB-A6D1-314B-A7C9-CD2858B93957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="34560" windowHeight="22340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-47280" yWindow="-4920" windowWidth="34560" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="80">
   <si>
     <t>State</t>
   </si>
@@ -316,10 +316,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E805"/>
+  <dimension ref="A1:E809"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="25" customWidth="1"/>
@@ -7897,7 +7896,7 @@
       <c r="D426" t="b">
         <v>1</v>
       </c>
-      <c r="E426" s="2" t="s">
+      <c r="E426" t="s">
         <v>79</v>
       </c>
     </row>
@@ -7914,7 +7913,7 @@
       <c r="D427" t="b">
         <v>1</v>
       </c>
-      <c r="E427" s="2" t="s">
+      <c r="E427" t="s">
         <v>79</v>
       </c>
     </row>
@@ -7957,16 +7956,16 @@
         <v>43</v>
       </c>
       <c r="B430">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C430" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D430" t="b">
         <v>1</v>
       </c>
       <c r="E430" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.2">
@@ -7974,27 +7973,27 @@
         <v>43</v>
       </c>
       <c r="B431">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C431" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D431" t="b">
         <v>1</v>
       </c>
       <c r="E431" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B432">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C432" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D432" t="b">
         <v>1</v>
@@ -8005,13 +8004,13 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B433">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C433" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D433" t="b">
         <v>1</v>
@@ -8022,36 +8021,36 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B434">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C434" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D434" t="b">
         <v>1</v>
       </c>
       <c r="E434" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B435">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C435" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D435" t="b">
         <v>1</v>
       </c>
       <c r="E435" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.2">
@@ -8059,7 +8058,7 @@
         <v>44</v>
       </c>
       <c r="B436">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C436" t="s">
         <v>9</v>
@@ -8076,7 +8075,7 @@
         <v>44</v>
       </c>
       <c r="B437">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C437" t="s">
         <v>14</v>
@@ -8093,7 +8092,7 @@
         <v>44</v>
       </c>
       <c r="B438">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C438" t="s">
         <v>10</v>
@@ -8110,7 +8109,7 @@
         <v>44</v>
       </c>
       <c r="B439">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C439" t="s">
         <v>13</v>
@@ -8124,10 +8123,10 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B440">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C440" t="s">
         <v>9</v>
@@ -8141,10 +8140,10 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B441">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C441" t="s">
         <v>14</v>
@@ -8158,10 +8157,10 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B442">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C442" t="s">
         <v>10</v>
@@ -8175,10 +8174,10 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B443">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C443" t="s">
         <v>13</v>
@@ -8195,7 +8194,7 @@
         <v>45</v>
       </c>
       <c r="B444">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C444" t="s">
         <v>9</v>
@@ -8212,7 +8211,7 @@
         <v>45</v>
       </c>
       <c r="B445">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C445" t="s">
         <v>14</v>
@@ -8229,7 +8228,7 @@
         <v>45</v>
       </c>
       <c r="B446">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C446" t="s">
         <v>10</v>
@@ -8246,7 +8245,7 @@
         <v>45</v>
       </c>
       <c r="B447">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C447" t="s">
         <v>13</v>
@@ -8260,47 +8259,47 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B448">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C448" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D448" t="b">
         <v>1</v>
       </c>
       <c r="E448" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B449">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C449" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D449" t="b">
         <v>1</v>
       </c>
       <c r="E449" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B450">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C450" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D450" t="b">
         <v>1</v>
@@ -8311,13 +8310,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B451">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C451" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D451" t="b">
         <v>1</v>
@@ -8331,7 +8330,7 @@
         <v>46</v>
       </c>
       <c r="B452">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C452" t="s">
         <v>6</v>
@@ -8348,7 +8347,7 @@
         <v>46</v>
       </c>
       <c r="B453">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C453" t="s">
         <v>26</v>
@@ -8365,16 +8364,16 @@
         <v>46</v>
       </c>
       <c r="B454">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C454" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D454" t="b">
         <v>1</v>
       </c>
       <c r="E454" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.2">
@@ -8382,16 +8381,16 @@
         <v>46</v>
       </c>
       <c r="B455">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C455" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D455" t="b">
         <v>1</v>
       </c>
       <c r="E455" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.2">
@@ -8399,16 +8398,16 @@
         <v>46</v>
       </c>
       <c r="B456">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C456" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D456" t="b">
         <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.2">
@@ -8416,16 +8415,16 @@
         <v>46</v>
       </c>
       <c r="B457">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C457" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D457" t="b">
         <v>1</v>
       </c>
       <c r="E457" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.2">
@@ -8433,16 +8432,16 @@
         <v>46</v>
       </c>
       <c r="B458">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C458" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D458" t="b">
         <v>1</v>
       </c>
       <c r="E458" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.2">
@@ -8450,16 +8449,16 @@
         <v>46</v>
       </c>
       <c r="B459">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C459" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D459" t="b">
         <v>1</v>
       </c>
       <c r="E459" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.2">
@@ -8470,7 +8469,7 @@
         <v>2012</v>
       </c>
       <c r="C460" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D460" t="b">
         <v>1</v>
@@ -8487,7 +8486,7 @@
         <v>2012</v>
       </c>
       <c r="C461" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D461" t="b">
         <v>1</v>
@@ -8501,16 +8500,16 @@
         <v>46</v>
       </c>
       <c r="B462">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C462" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D462" t="b">
         <v>1</v>
       </c>
       <c r="E462" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.2">
@@ -8518,16 +8517,16 @@
         <v>46</v>
       </c>
       <c r="B463">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C463" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D463" t="b">
         <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.2">
@@ -8535,10 +8534,10 @@
         <v>46</v>
       </c>
       <c r="B464">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C464" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D464" t="b">
         <v>1</v>
@@ -8552,10 +8551,10 @@
         <v>46</v>
       </c>
       <c r="B465">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C465" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D465" t="b">
         <v>1</v>
@@ -8569,16 +8568,16 @@
         <v>46</v>
       </c>
       <c r="B466">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C466" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D466" t="b">
         <v>1</v>
       </c>
       <c r="E466" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.2">
@@ -8586,16 +8585,16 @@
         <v>46</v>
       </c>
       <c r="B467">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C467" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D467" t="b">
         <v>1</v>
       </c>
       <c r="E467" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.2">
@@ -8606,7 +8605,7 @@
         <v>2016</v>
       </c>
       <c r="C468" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D468" t="b">
         <v>1</v>
@@ -8623,7 +8622,7 @@
         <v>2016</v>
       </c>
       <c r="C469" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D469" t="b">
         <v>1</v>
@@ -8637,16 +8636,16 @@
         <v>46</v>
       </c>
       <c r="B470">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C470" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D470" t="b">
         <v>1</v>
       </c>
       <c r="E470" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.2">
@@ -8654,16 +8653,16 @@
         <v>46</v>
       </c>
       <c r="B471">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C471" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D471" t="b">
         <v>1</v>
       </c>
       <c r="E471" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.2">
@@ -8671,7 +8670,7 @@
         <v>46</v>
       </c>
       <c r="B472">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C472" t="s">
         <v>6</v>
@@ -8688,7 +8687,7 @@
         <v>46</v>
       </c>
       <c r="B473">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C473" t="s">
         <v>26</v>
@@ -8705,7 +8704,7 @@
         <v>46</v>
       </c>
       <c r="B474">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C474" t="s">
         <v>6</v>
@@ -8722,7 +8721,7 @@
         <v>46</v>
       </c>
       <c r="B475">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C475" t="s">
         <v>26</v>
@@ -8736,13 +8735,13 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B476">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C476" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D476" t="b">
         <v>1</v>
@@ -8753,13 +8752,13 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B477">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C477" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D477" t="b">
         <v>1</v>
@@ -8770,36 +8769,36 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B478">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C478" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D478" t="b">
         <v>1</v>
       </c>
       <c r="E478" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B479">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C479" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D479" t="b">
         <v>1</v>
       </c>
       <c r="E479" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.2">
@@ -8807,7 +8806,7 @@
         <v>48</v>
       </c>
       <c r="B480">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C480" t="s">
         <v>9</v>
@@ -8824,7 +8823,7 @@
         <v>48</v>
       </c>
       <c r="B481">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C481" t="s">
         <v>14</v>
@@ -8841,7 +8840,7 @@
         <v>48</v>
       </c>
       <c r="B482">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C482" t="s">
         <v>10</v>
@@ -8858,7 +8857,7 @@
         <v>48</v>
       </c>
       <c r="B483">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C483" t="s">
         <v>13</v>
@@ -8872,10 +8871,10 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B484">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C484" t="s">
         <v>9</v>
@@ -8884,15 +8883,15 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B485">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C485" t="s">
         <v>14</v>
@@ -8901,15 +8900,15 @@
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B486">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C486" t="s">
         <v>10</v>
@@ -8923,10 +8922,10 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B487">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C487" t="s">
         <v>13</v>
@@ -8943,7 +8942,7 @@
         <v>49</v>
       </c>
       <c r="B488">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C488" t="s">
         <v>9</v>
@@ -8960,7 +8959,7 @@
         <v>49</v>
       </c>
       <c r="B489">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C489" t="s">
         <v>14</v>
@@ -8977,7 +8976,7 @@
         <v>49</v>
       </c>
       <c r="B490">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C490" t="s">
         <v>10</v>
@@ -8994,7 +8993,7 @@
         <v>49</v>
       </c>
       <c r="B491">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C491" t="s">
         <v>13</v>
@@ -9011,7 +9010,7 @@
         <v>49</v>
       </c>
       <c r="B492">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C492" t="s">
         <v>9</v>
@@ -9028,7 +9027,7 @@
         <v>49</v>
       </c>
       <c r="B493">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C493" t="s">
         <v>14</v>
@@ -9045,7 +9044,7 @@
         <v>49</v>
       </c>
       <c r="B494">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C494" t="s">
         <v>10</v>
@@ -9062,7 +9061,7 @@
         <v>49</v>
       </c>
       <c r="B495">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C495" t="s">
         <v>13</v>
@@ -9079,7 +9078,7 @@
         <v>49</v>
       </c>
       <c r="B496">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C496" t="s">
         <v>9</v>
@@ -9096,7 +9095,7 @@
         <v>49</v>
       </c>
       <c r="B497">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C497" t="s">
         <v>14</v>
@@ -9113,7 +9112,7 @@
         <v>49</v>
       </c>
       <c r="B498">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C498" t="s">
         <v>10</v>
@@ -9130,7 +9129,7 @@
         <v>49</v>
       </c>
       <c r="B499">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C499" t="s">
         <v>13</v>
@@ -9147,7 +9146,7 @@
         <v>49</v>
       </c>
       <c r="B500">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C500" t="s">
         <v>9</v>
@@ -9164,7 +9163,7 @@
         <v>49</v>
       </c>
       <c r="B501">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C501" t="s">
         <v>14</v>
@@ -9181,7 +9180,7 @@
         <v>49</v>
       </c>
       <c r="B502">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C502" t="s">
         <v>10</v>
@@ -9198,7 +9197,7 @@
         <v>49</v>
       </c>
       <c r="B503">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C503" t="s">
         <v>13</v>
@@ -9212,47 +9211,47 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B504">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C504" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D504" t="b">
         <v>1</v>
       </c>
       <c r="E504" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B505">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C505" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D505" t="b">
         <v>1</v>
       </c>
       <c r="E505" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B506">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C506" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D506" t="b">
         <v>1</v>
@@ -9263,13 +9262,13 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B507">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C507" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D507" t="b">
         <v>1</v>
@@ -9283,16 +9282,16 @@
         <v>50</v>
       </c>
       <c r="B508">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C508" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D508" t="b">
         <v>1</v>
       </c>
       <c r="E508" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.2">
@@ -9300,16 +9299,16 @@
         <v>50</v>
       </c>
       <c r="B509">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C509" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D509" t="b">
         <v>1</v>
       </c>
       <c r="E509" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.2">
@@ -9317,16 +9316,16 @@
         <v>50</v>
       </c>
       <c r="B510">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C510" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D510" t="b">
         <v>1</v>
       </c>
       <c r="E510" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.2">
@@ -9334,16 +9333,16 @@
         <v>50</v>
       </c>
       <c r="B511">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C511" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D511" t="b">
         <v>1</v>
       </c>
       <c r="E511" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.2">
@@ -9354,13 +9353,13 @@
         <v>2010</v>
       </c>
       <c r="C512" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D512" t="b">
         <v>1</v>
       </c>
       <c r="E512" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.2">
@@ -9371,13 +9370,13 @@
         <v>2010</v>
       </c>
       <c r="C513" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D513" t="b">
         <v>1</v>
       </c>
       <c r="E513" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.2">
@@ -9388,13 +9387,13 @@
         <v>2010</v>
       </c>
       <c r="C514" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D514" t="b">
         <v>1</v>
       </c>
       <c r="E514" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.2">
@@ -9405,13 +9404,13 @@
         <v>2010</v>
       </c>
       <c r="C515" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D515" t="b">
         <v>1</v>
       </c>
       <c r="E515" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.2">
@@ -9419,16 +9418,16 @@
         <v>50</v>
       </c>
       <c r="B516">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C516" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D516" t="b">
         <v>1</v>
       </c>
       <c r="E516" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.2">
@@ -9436,16 +9435,16 @@
         <v>50</v>
       </c>
       <c r="B517">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C517" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D517" t="b">
         <v>1</v>
       </c>
       <c r="E517" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.2">
@@ -9453,16 +9452,16 @@
         <v>50</v>
       </c>
       <c r="B518">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C518" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D518" t="b">
         <v>1</v>
       </c>
       <c r="E518" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.2">
@@ -9470,16 +9469,16 @@
         <v>50</v>
       </c>
       <c r="B519">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C519" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D519" t="b">
         <v>1</v>
       </c>
       <c r="E519" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.2">
@@ -9490,13 +9489,13 @@
         <v>2012</v>
       </c>
       <c r="C520" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D520" t="b">
         <v>1</v>
       </c>
       <c r="E520" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.2">
@@ -9507,13 +9506,13 @@
         <v>2012</v>
       </c>
       <c r="C521" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D521" t="b">
         <v>1</v>
       </c>
       <c r="E521" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.2">
@@ -9524,13 +9523,13 @@
         <v>2012</v>
       </c>
       <c r="C522" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D522" t="b">
         <v>1</v>
       </c>
       <c r="E522" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.2">
@@ -9541,13 +9540,13 @@
         <v>2012</v>
       </c>
       <c r="C523" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D523" t="b">
         <v>1</v>
       </c>
       <c r="E523" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.2">
@@ -9555,16 +9554,16 @@
         <v>50</v>
       </c>
       <c r="B524">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C524" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D524" t="b">
         <v>1</v>
       </c>
       <c r="E524" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.2">
@@ -9572,16 +9571,16 @@
         <v>50</v>
       </c>
       <c r="B525">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C525" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D525" t="b">
         <v>1</v>
       </c>
       <c r="E525" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.2">
@@ -9589,16 +9588,16 @@
         <v>50</v>
       </c>
       <c r="B526">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C526" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D526" t="b">
         <v>1</v>
       </c>
       <c r="E526" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.2">
@@ -9606,16 +9605,16 @@
         <v>50</v>
       </c>
       <c r="B527">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C527" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D527" t="b">
         <v>1</v>
       </c>
       <c r="E527" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.2">
@@ -9626,13 +9625,13 @@
         <v>2014</v>
       </c>
       <c r="C528" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D528" t="b">
         <v>1</v>
       </c>
       <c r="E528" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.2">
@@ -9643,13 +9642,13 @@
         <v>2014</v>
       </c>
       <c r="C529" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D529" t="b">
         <v>1</v>
       </c>
       <c r="E529" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.2">
@@ -9660,13 +9659,13 @@
         <v>2014</v>
       </c>
       <c r="C530" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D530" t="b">
         <v>1</v>
       </c>
       <c r="E530" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.2">
@@ -9677,13 +9676,13 @@
         <v>2014</v>
       </c>
       <c r="C531" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D531" t="b">
         <v>1</v>
       </c>
       <c r="E531" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
@@ -9691,16 +9690,16 @@
         <v>50</v>
       </c>
       <c r="B532">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C532" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D532" t="b">
         <v>1</v>
       </c>
       <c r="E532" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.2">
@@ -9708,16 +9707,16 @@
         <v>50</v>
       </c>
       <c r="B533">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C533" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D533" t="b">
         <v>1</v>
       </c>
       <c r="E533" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.2">
@@ -9725,16 +9724,16 @@
         <v>50</v>
       </c>
       <c r="B534">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C534" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D534" t="b">
         <v>1</v>
       </c>
       <c r="E534" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.2">
@@ -9742,16 +9741,16 @@
         <v>50</v>
       </c>
       <c r="B535">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C535" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D535" t="b">
         <v>1</v>
       </c>
       <c r="E535" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.2">
@@ -9762,13 +9761,13 @@
         <v>2016</v>
       </c>
       <c r="C536" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D536" t="b">
         <v>1</v>
       </c>
       <c r="E536" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.2">
@@ -9779,13 +9778,13 @@
         <v>2016</v>
       </c>
       <c r="C537" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D537" t="b">
         <v>1</v>
       </c>
       <c r="E537" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.2">
@@ -9796,13 +9795,13 @@
         <v>2016</v>
       </c>
       <c r="C538" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D538" t="b">
         <v>1</v>
       </c>
       <c r="E538" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.2">
@@ -9813,24 +9812,24 @@
         <v>2016</v>
       </c>
       <c r="C539" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D539" t="b">
         <v>1</v>
       </c>
       <c r="E539" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B540">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C540" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D540" t="b">
         <v>1</v>
@@ -9841,13 +9840,13 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B541">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C541" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D541" t="b">
         <v>1</v>
@@ -9858,13 +9857,13 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B542">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C542" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D542" t="b">
         <v>1</v>
@@ -9875,13 +9874,13 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B543">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C543" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D543" t="b">
         <v>1</v>
@@ -9895,10 +9894,10 @@
         <v>51</v>
       </c>
       <c r="B544">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C544" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D544" t="b">
         <v>1</v>
@@ -9912,10 +9911,10 @@
         <v>51</v>
       </c>
       <c r="B545">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C545" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D545" t="b">
         <v>1</v>
@@ -9929,10 +9928,10 @@
         <v>51</v>
       </c>
       <c r="B546">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C546" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D546" t="b">
         <v>1</v>
@@ -9946,10 +9945,10 @@
         <v>51</v>
       </c>
       <c r="B547">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C547" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D547" t="b">
         <v>1</v>
@@ -9963,10 +9962,10 @@
         <v>51</v>
       </c>
       <c r="B548">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C548" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D548" t="b">
         <v>1</v>
@@ -9980,10 +9979,10 @@
         <v>51</v>
       </c>
       <c r="B549">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C549" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D549" t="b">
         <v>1</v>
@@ -9997,7 +9996,7 @@
         <v>51</v>
       </c>
       <c r="B550">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -10014,7 +10013,7 @@
         <v>51</v>
       </c>
       <c r="B551">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C551" t="s">
         <v>27</v>
@@ -10031,10 +10030,10 @@
         <v>51</v>
       </c>
       <c r="B552">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C552" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D552" t="b">
         <v>1</v>
@@ -10048,10 +10047,10 @@
         <v>51</v>
       </c>
       <c r="B553">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C553" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D553" t="b">
         <v>1</v>
@@ -10062,70 +10061,70 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B554">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="C554" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D554" t="b">
         <v>1</v>
       </c>
       <c r="E554" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B555">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="C555" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D555" t="b">
         <v>1</v>
       </c>
       <c r="E555" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B556">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C556" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D556" t="b">
         <v>1</v>
       </c>
       <c r="E556" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B557">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C557" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D557" t="b">
         <v>1</v>
       </c>
       <c r="E557" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.2">
@@ -10133,16 +10132,16 @@
         <v>52</v>
       </c>
       <c r="B558">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C558" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D558" t="b">
         <v>1</v>
       </c>
       <c r="E558" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.2">
@@ -10150,16 +10149,16 @@
         <v>52</v>
       </c>
       <c r="B559">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C559" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D559" t="b">
         <v>1</v>
       </c>
       <c r="E559" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.2">
@@ -10167,7 +10166,7 @@
         <v>52</v>
       </c>
       <c r="B560">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C560" t="s">
         <v>10</v>
@@ -10184,7 +10183,7 @@
         <v>52</v>
       </c>
       <c r="B561">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C561" t="s">
         <v>13</v>
@@ -10201,16 +10200,16 @@
         <v>52</v>
       </c>
       <c r="B562">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C562" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D562" t="b">
         <v>1</v>
       </c>
       <c r="E562" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.2">
@@ -10218,16 +10217,16 @@
         <v>52</v>
       </c>
       <c r="B563">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C563" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D563" t="b">
         <v>1</v>
       </c>
       <c r="E563" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.2">
@@ -10235,16 +10234,16 @@
         <v>52</v>
       </c>
       <c r="B564">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C564" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D564" t="b">
         <v>1</v>
       </c>
       <c r="E564" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
@@ -10252,16 +10251,16 @@
         <v>52</v>
       </c>
       <c r="B565">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C565" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D565" t="b">
         <v>1</v>
       </c>
       <c r="E565" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.2">
@@ -10269,7 +10268,7 @@
         <v>52</v>
       </c>
       <c r="B566">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C566" t="s">
         <v>10</v>
@@ -10286,7 +10285,7 @@
         <v>52</v>
       </c>
       <c r="B567">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C567" t="s">
         <v>13</v>
@@ -10303,16 +10302,16 @@
         <v>52</v>
       </c>
       <c r="B568">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C568" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D568" t="b">
         <v>1</v>
       </c>
       <c r="E568" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.2">
@@ -10320,58 +10319,58 @@
         <v>52</v>
       </c>
       <c r="B569">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C569" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D569" t="b">
         <v>1</v>
       </c>
       <c r="E569" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B570">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C570" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D570" t="b">
         <v>1</v>
       </c>
       <c r="E570" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B571">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C571" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D571" t="b">
         <v>1</v>
       </c>
       <c r="E571" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B572">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C572" t="s">
         <v>10</v>
@@ -10380,15 +10379,15 @@
         <v>1</v>
       </c>
       <c r="E572" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B573">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C573" t="s">
         <v>13</v>
@@ -10397,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="E573" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.2">
@@ -10405,10 +10404,10 @@
         <v>53</v>
       </c>
       <c r="B574">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C574" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D574" t="b">
         <v>1</v>
@@ -10422,10 +10421,10 @@
         <v>53</v>
       </c>
       <c r="B575">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C575" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D575" t="b">
         <v>1</v>
@@ -10439,10 +10438,10 @@
         <v>53</v>
       </c>
       <c r="B576">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C576" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D576" t="b">
         <v>1</v>
@@ -10456,10 +10455,10 @@
         <v>53</v>
       </c>
       <c r="B577">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C577" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D577" t="b">
         <v>1</v>
@@ -10473,10 +10472,10 @@
         <v>53</v>
       </c>
       <c r="B578">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C578" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D578" t="b">
         <v>1</v>
@@ -10490,10 +10489,10 @@
         <v>53</v>
       </c>
       <c r="B579">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C579" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D579" t="b">
         <v>1</v>
@@ -10504,10 +10503,10 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B580">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C580" t="s">
         <v>9</v>
@@ -10521,10 +10520,10 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B581">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C581" t="s">
         <v>14</v>
@@ -10538,10 +10537,10 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B582">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C582" t="s">
         <v>10</v>
@@ -10555,10 +10554,10 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B583">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C583" t="s">
         <v>13</v>
@@ -10575,7 +10574,7 @@
         <v>54</v>
       </c>
       <c r="B584">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C584" t="s">
         <v>9</v>
@@ -10592,7 +10591,7 @@
         <v>54</v>
       </c>
       <c r="B585">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C585" t="s">
         <v>14</v>
@@ -10609,7 +10608,7 @@
         <v>54</v>
       </c>
       <c r="B586">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C586" t="s">
         <v>10</v>
@@ -10626,7 +10625,7 @@
         <v>54</v>
       </c>
       <c r="B587">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C587" t="s">
         <v>13</v>
@@ -10640,10 +10639,10 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B588">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C588" t="s">
         <v>9</v>
@@ -10657,10 +10656,10 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B589">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C589" t="s">
         <v>14</v>
@@ -10674,10 +10673,10 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B590">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C590" t="s">
         <v>10</v>
@@ -10691,10 +10690,10 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B591">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C591" t="s">
         <v>13</v>
@@ -10711,7 +10710,7 @@
         <v>55</v>
       </c>
       <c r="B592">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C592" t="s">
         <v>9</v>
@@ -10728,7 +10727,7 @@
         <v>55</v>
       </c>
       <c r="B593">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C593" t="s">
         <v>14</v>
@@ -10745,7 +10744,7 @@
         <v>55</v>
       </c>
       <c r="B594">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C594" t="s">
         <v>10</v>
@@ -10762,7 +10761,7 @@
         <v>55</v>
       </c>
       <c r="B595">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C595" t="s">
         <v>13</v>
@@ -10776,47 +10775,47 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B596">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C596" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D596" t="b">
         <v>1</v>
       </c>
       <c r="E596" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B597">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C597" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D597" t="b">
         <v>1</v>
       </c>
       <c r="E597" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B598">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C598" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D598" t="b">
         <v>1</v>
@@ -10827,13 +10826,13 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B599">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C599" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D599" t="b">
         <v>1</v>
@@ -10847,7 +10846,7 @@
         <v>56</v>
       </c>
       <c r="B600">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C600" t="s">
         <v>10</v>
@@ -10864,7 +10863,7 @@
         <v>56</v>
       </c>
       <c r="B601">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C601" t="s">
         <v>13</v>
@@ -10881,10 +10880,10 @@
         <v>56</v>
       </c>
       <c r="B602">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C602" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D602" t="b">
         <v>1</v>
@@ -10898,10 +10897,10 @@
         <v>56</v>
       </c>
       <c r="B603">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C603" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D603" t="b">
         <v>1</v>
@@ -10915,7 +10914,7 @@
         <v>56</v>
       </c>
       <c r="B604">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C604" t="s">
         <v>10</v>
@@ -10924,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="E604" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.2">
@@ -10932,7 +10931,7 @@
         <v>56</v>
       </c>
       <c r="B605">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C605" t="s">
         <v>13</v>
@@ -10941,7 +10940,7 @@
         <v>1</v>
       </c>
       <c r="E605" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.2">
@@ -10949,7 +10948,7 @@
         <v>56</v>
       </c>
       <c r="B606">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C606" t="s">
         <v>9</v>
@@ -10958,7 +10957,7 @@
         <v>1</v>
       </c>
       <c r="E606" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.2">
@@ -10966,7 +10965,7 @@
         <v>56</v>
       </c>
       <c r="B607">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C607" t="s">
         <v>14</v>
@@ -10975,7 +10974,7 @@
         <v>1</v>
       </c>
       <c r="E607" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.2">
@@ -10983,7 +10982,7 @@
         <v>56</v>
       </c>
       <c r="B608">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C608" t="s">
         <v>10</v>
@@ -10992,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="E608" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.2">
@@ -11000,7 +10999,7 @@
         <v>56</v>
       </c>
       <c r="B609">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C609" t="s">
         <v>13</v>
@@ -11009,7 +11008,7 @@
         <v>1</v>
       </c>
       <c r="E609" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.2">
@@ -11017,7 +11016,7 @@
         <v>56</v>
       </c>
       <c r="B610">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C610" t="s">
         <v>9</v>
@@ -11026,7 +11025,7 @@
         <v>1</v>
       </c>
       <c r="E610" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.2">
@@ -11034,7 +11033,7 @@
         <v>56</v>
       </c>
       <c r="B611">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C611" t="s">
         <v>14</v>
@@ -11043,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="E611" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.2">
@@ -11051,7 +11050,7 @@
         <v>56</v>
       </c>
       <c r="B612">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C612" t="s">
         <v>10</v>
@@ -11060,7 +11059,7 @@
         <v>1</v>
       </c>
       <c r="E612" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.2">
@@ -11068,7 +11067,7 @@
         <v>56</v>
       </c>
       <c r="B613">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C613" t="s">
         <v>13</v>
@@ -11077,15 +11076,15 @@
         <v>1</v>
       </c>
       <c r="E613" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B614">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C614" t="s">
         <v>9</v>
@@ -11099,10 +11098,10 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B615">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C615" t="s">
         <v>14</v>
@@ -11116,10 +11115,10 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B616">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C616" t="s">
         <v>10</v>
@@ -11133,10 +11132,10 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B617">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C617" t="s">
         <v>13</v>
@@ -11153,7 +11152,7 @@
         <v>58</v>
       </c>
       <c r="B618">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C618" t="s">
         <v>9</v>
@@ -11170,7 +11169,7 @@
         <v>58</v>
       </c>
       <c r="B619">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C619" t="s">
         <v>14</v>
@@ -11187,7 +11186,7 @@
         <v>58</v>
       </c>
       <c r="B620">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C620" t="s">
         <v>10</v>
@@ -11204,7 +11203,7 @@
         <v>58</v>
       </c>
       <c r="B621">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C621" t="s">
         <v>13</v>
@@ -11221,7 +11220,7 @@
         <v>58</v>
       </c>
       <c r="B622">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C622" t="s">
         <v>9</v>
@@ -11238,7 +11237,7 @@
         <v>58</v>
       </c>
       <c r="B623">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C623" t="s">
         <v>14</v>
@@ -11255,7 +11254,7 @@
         <v>58</v>
       </c>
       <c r="B624">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C624" t="s">
         <v>10</v>
@@ -11272,7 +11271,7 @@
         <v>58</v>
       </c>
       <c r="B625">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C625" t="s">
         <v>13</v>
@@ -11286,10 +11285,10 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B626">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C626" t="s">
         <v>9</v>
@@ -11303,10 +11302,10 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B627">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C627" t="s">
         <v>14</v>
@@ -11320,10 +11319,10 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B628">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C628" t="s">
         <v>10</v>
@@ -11332,15 +11331,15 @@
         <v>1</v>
       </c>
       <c r="E628" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B629">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C629" t="s">
         <v>13</v>
@@ -11349,7 +11348,7 @@
         <v>1</v>
       </c>
       <c r="E629" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.2">
@@ -11357,7 +11356,7 @@
         <v>59</v>
       </c>
       <c r="B630">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C630" t="s">
         <v>9</v>
@@ -11374,7 +11373,7 @@
         <v>59</v>
       </c>
       <c r="B631">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C631" t="s">
         <v>14</v>
@@ -11391,7 +11390,7 @@
         <v>59</v>
       </c>
       <c r="B632">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C632" t="s">
         <v>10</v>
@@ -11408,7 +11407,7 @@
         <v>59</v>
       </c>
       <c r="B633">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C633" t="s">
         <v>13</v>
@@ -11425,16 +11424,16 @@
         <v>59</v>
       </c>
       <c r="B634">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C634" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D634" t="b">
         <v>1</v>
       </c>
       <c r="E634" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.2">
@@ -11442,16 +11441,16 @@
         <v>59</v>
       </c>
       <c r="B635">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C635" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D635" t="b">
         <v>1</v>
       </c>
       <c r="E635" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.2">
@@ -11459,16 +11458,16 @@
         <v>59</v>
       </c>
       <c r="B636">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C636" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D636" t="b">
         <v>1</v>
       </c>
       <c r="E636" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.2">
@@ -11476,16 +11475,16 @@
         <v>59</v>
       </c>
       <c r="B637">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C637" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D637" t="b">
         <v>1</v>
       </c>
       <c r="E637" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.2">
@@ -11493,7 +11492,7 @@
         <v>59</v>
       </c>
       <c r="B638">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C638" t="s">
         <v>10</v>
@@ -11510,7 +11509,7 @@
         <v>59</v>
       </c>
       <c r="B639">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C639" t="s">
         <v>13</v>
@@ -11527,16 +11526,16 @@
         <v>59</v>
       </c>
       <c r="B640">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C640" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D640" t="b">
         <v>1</v>
       </c>
       <c r="E640" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.2">
@@ -11544,58 +11543,58 @@
         <v>59</v>
       </c>
       <c r="B641">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C641" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D641" t="b">
         <v>1</v>
       </c>
       <c r="E641" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B642">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C642" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D642" t="b">
         <v>1</v>
       </c>
       <c r="E642" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B643">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C643" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D643" t="b">
         <v>1</v>
       </c>
       <c r="E643" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B644">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C644" t="s">
         <v>10</v>
@@ -11604,15 +11603,15 @@
         <v>1</v>
       </c>
       <c r="E644" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B645">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C645" t="s">
         <v>13</v>
@@ -11621,7 +11620,7 @@
         <v>1</v>
       </c>
       <c r="E645" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.2">
@@ -11629,7 +11628,7 @@
         <v>60</v>
       </c>
       <c r="B646">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C646" t="s">
         <v>9</v>
@@ -11646,7 +11645,7 @@
         <v>60</v>
       </c>
       <c r="B647">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C647" t="s">
         <v>14</v>
@@ -11663,7 +11662,7 @@
         <v>60</v>
       </c>
       <c r="B648">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C648" t="s">
         <v>10</v>
@@ -11680,7 +11679,7 @@
         <v>60</v>
       </c>
       <c r="B649">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C649" t="s">
         <v>13</v>
@@ -11694,13 +11693,13 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B650">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C650" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D650" t="b">
         <v>1</v>
@@ -11711,13 +11710,13 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B651">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C651" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D651" t="b">
         <v>1</v>
@@ -11728,13 +11727,13 @@
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B652">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C652" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D652" t="b">
         <v>1</v>
@@ -11745,13 +11744,13 @@
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B653">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C653" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D653" t="b">
         <v>1</v>
@@ -11765,10 +11764,10 @@
         <v>61</v>
       </c>
       <c r="B654">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C654" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D654" t="b">
         <v>1</v>
@@ -11782,10 +11781,10 @@
         <v>61</v>
       </c>
       <c r="B655">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C655" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D655" t="b">
         <v>1</v>
@@ -11799,10 +11798,10 @@
         <v>61</v>
       </c>
       <c r="B656">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C656" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D656" t="b">
         <v>1</v>
@@ -11816,10 +11815,10 @@
         <v>61</v>
       </c>
       <c r="B657">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C657" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D657" t="b">
         <v>1</v>
@@ -11833,7 +11832,7 @@
         <v>61</v>
       </c>
       <c r="B658">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C658" t="s">
         <v>9</v>
@@ -11850,7 +11849,7 @@
         <v>61</v>
       </c>
       <c r="B659">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C659" t="s">
         <v>14</v>
@@ -11867,7 +11866,7 @@
         <v>61</v>
       </c>
       <c r="B660">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C660" t="s">
         <v>10</v>
@@ -11884,7 +11883,7 @@
         <v>61</v>
       </c>
       <c r="B661">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C661" t="s">
         <v>13</v>
@@ -11898,10 +11897,10 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B662">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C662" t="s">
         <v>9</v>
@@ -11915,10 +11914,10 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B663">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C663" t="s">
         <v>14</v>
@@ -11932,10 +11931,10 @@
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B664">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C664" t="s">
         <v>10</v>
@@ -11949,10 +11948,10 @@
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B665">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C665" t="s">
         <v>13</v>
@@ -11969,7 +11968,7 @@
         <v>62</v>
       </c>
       <c r="B666">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C666" t="s">
         <v>9</v>
@@ -11986,7 +11985,7 @@
         <v>62</v>
       </c>
       <c r="B667">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C667" t="s">
         <v>14</v>
@@ -12003,7 +12002,7 @@
         <v>62</v>
       </c>
       <c r="B668">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C668" t="s">
         <v>10</v>
@@ -12020,7 +12019,7 @@
         <v>62</v>
       </c>
       <c r="B669">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C669" t="s">
         <v>13</v>
@@ -12034,10 +12033,10 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B670">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C670" t="s">
         <v>9</v>
@@ -12046,15 +12045,15 @@
         <v>1</v>
       </c>
       <c r="E670" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B671">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C671" t="s">
         <v>14</v>
@@ -12063,15 +12062,15 @@
         <v>1</v>
       </c>
       <c r="E671" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B672">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C672" t="s">
         <v>10</v>
@@ -12080,15 +12079,15 @@
         <v>1</v>
       </c>
       <c r="E672" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B673">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C673" t="s">
         <v>13</v>
@@ -12097,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="E673" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.2">
@@ -12105,7 +12104,7 @@
         <v>63</v>
       </c>
       <c r="B674">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C674" t="s">
         <v>9</v>
@@ -12122,7 +12121,7 @@
         <v>63</v>
       </c>
       <c r="B675">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C675" t="s">
         <v>14</v>
@@ -12139,7 +12138,7 @@
         <v>63</v>
       </c>
       <c r="B676">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C676" t="s">
         <v>10</v>
@@ -12156,7 +12155,7 @@
         <v>63</v>
       </c>
       <c r="B677">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C677" t="s">
         <v>13</v>
@@ -12173,7 +12172,7 @@
         <v>63</v>
       </c>
       <c r="B678">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C678" t="s">
         <v>9</v>
@@ -12190,7 +12189,7 @@
         <v>63</v>
       </c>
       <c r="B679">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C679" t="s">
         <v>14</v>
@@ -12207,7 +12206,7 @@
         <v>63</v>
       </c>
       <c r="B680">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C680" t="s">
         <v>10</v>
@@ -12224,7 +12223,7 @@
         <v>63</v>
       </c>
       <c r="B681">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C681" t="s">
         <v>13</v>
@@ -12241,7 +12240,7 @@
         <v>63</v>
       </c>
       <c r="B682">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C682" t="s">
         <v>9</v>
@@ -12258,7 +12257,7 @@
         <v>63</v>
       </c>
       <c r="B683">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C683" t="s">
         <v>14</v>
@@ -12275,7 +12274,7 @@
         <v>63</v>
       </c>
       <c r="B684">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C684" t="s">
         <v>10</v>
@@ -12292,7 +12291,7 @@
         <v>63</v>
       </c>
       <c r="B685">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C685" t="s">
         <v>13</v>
@@ -12309,7 +12308,7 @@
         <v>63</v>
       </c>
       <c r="B686">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C686" t="s">
         <v>9</v>
@@ -12326,7 +12325,7 @@
         <v>63</v>
       </c>
       <c r="B687">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C687" t="s">
         <v>14</v>
@@ -12343,7 +12342,7 @@
         <v>63</v>
       </c>
       <c r="B688">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C688" t="s">
         <v>10</v>
@@ -12360,7 +12359,7 @@
         <v>63</v>
       </c>
       <c r="B689">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C689" t="s">
         <v>13</v>
@@ -12374,13 +12373,13 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B690">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C690" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D690" t="b">
         <v>1</v>
@@ -12391,13 +12390,13 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B691">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C691" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D691" t="b">
         <v>1</v>
@@ -12408,10 +12407,10 @@
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B692">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C692" t="s">
         <v>10</v>
@@ -12425,10 +12424,10 @@
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B693">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C693" t="s">
         <v>13</v>
@@ -12445,16 +12444,16 @@
         <v>64</v>
       </c>
       <c r="B694">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C694" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D694" t="b">
         <v>1</v>
       </c>
       <c r="E694" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.2">
@@ -12462,16 +12461,16 @@
         <v>64</v>
       </c>
       <c r="B695">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C695" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D695" t="b">
         <v>1</v>
       </c>
       <c r="E695" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.2">
@@ -12479,7 +12478,7 @@
         <v>64</v>
       </c>
       <c r="B696">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C696" t="s">
         <v>10</v>
@@ -12488,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="E696" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.2">
@@ -12496,7 +12495,7 @@
         <v>64</v>
       </c>
       <c r="B697">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C697" t="s">
         <v>13</v>
@@ -12505,7 +12504,7 @@
         <v>1</v>
       </c>
       <c r="E697" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.2">
@@ -12513,16 +12512,16 @@
         <v>64</v>
       </c>
       <c r="B698">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C698" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D698" t="b">
         <v>1</v>
       </c>
       <c r="E698" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.2">
@@ -12530,16 +12529,16 @@
         <v>64</v>
       </c>
       <c r="B699">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C699" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D699" t="b">
         <v>1</v>
       </c>
       <c r="E699" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.2">
@@ -12547,10 +12546,10 @@
         <v>64</v>
       </c>
       <c r="B700">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C700" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D700" t="b">
         <v>1</v>
@@ -12564,10 +12563,10 @@
         <v>64</v>
       </c>
       <c r="B701">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C701" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D701" t="b">
         <v>1</v>
@@ -12581,7 +12580,7 @@
         <v>64</v>
       </c>
       <c r="B702">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C702" t="s">
         <v>10</v>
@@ -12590,7 +12589,7 @@
         <v>1</v>
       </c>
       <c r="E702" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.2">
@@ -12598,7 +12597,7 @@
         <v>64</v>
       </c>
       <c r="B703">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C703" t="s">
         <v>13</v>
@@ -12607,15 +12606,15 @@
         <v>1</v>
       </c>
       <c r="E703" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B704">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C704" t="s">
         <v>9</v>
@@ -12629,10 +12628,10 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B705">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C705" t="s">
         <v>14</v>
@@ -12646,10 +12645,10 @@
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B706">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C706" t="s">
         <v>10</v>
@@ -12658,15 +12657,15 @@
         <v>1</v>
       </c>
       <c r="E706" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B707">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C707" t="s">
         <v>13</v>
@@ -12675,7 +12674,7 @@
         <v>1</v>
       </c>
       <c r="E707" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.2">
@@ -12683,16 +12682,16 @@
         <v>65</v>
       </c>
       <c r="B708">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C708" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D708" t="b">
         <v>1</v>
       </c>
       <c r="E708" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.2">
@@ -12700,16 +12699,16 @@
         <v>65</v>
       </c>
       <c r="B709">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C709" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D709" t="b">
         <v>1</v>
       </c>
       <c r="E709" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.2">
@@ -12717,7 +12716,7 @@
         <v>65</v>
       </c>
       <c r="B710">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C710" t="s">
         <v>10</v>
@@ -12734,7 +12733,7 @@
         <v>65</v>
       </c>
       <c r="B711">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C711" t="s">
         <v>13</v>
@@ -12751,7 +12750,7 @@
         <v>65</v>
       </c>
       <c r="B712">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C712" t="s">
         <v>10</v>
@@ -12768,7 +12767,7 @@
         <v>65</v>
       </c>
       <c r="B713">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C713" t="s">
         <v>13</v>
@@ -12785,7 +12784,7 @@
         <v>65</v>
       </c>
       <c r="B714">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C714" t="s">
         <v>10</v>
@@ -12802,7 +12801,7 @@
         <v>65</v>
       </c>
       <c r="B715">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C715" t="s">
         <v>13</v>
@@ -12819,7 +12818,7 @@
         <v>65</v>
       </c>
       <c r="B716">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C716" t="s">
         <v>10</v>
@@ -12836,7 +12835,7 @@
         <v>65</v>
       </c>
       <c r="B717">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C717" t="s">
         <v>13</v>
@@ -12853,7 +12852,7 @@
         <v>65</v>
       </c>
       <c r="B718">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C718" t="s">
         <v>10</v>
@@ -12870,7 +12869,7 @@
         <v>65</v>
       </c>
       <c r="B719">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C719" t="s">
         <v>13</v>
@@ -12884,70 +12883,70 @@
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B720">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C720" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D720" t="b">
         <v>1</v>
       </c>
       <c r="E720" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B721">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C721" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D721" t="b">
         <v>1</v>
       </c>
       <c r="E721" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B722">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C722" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D722" t="b">
         <v>1</v>
       </c>
       <c r="E722" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B723">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C723" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D723" t="b">
         <v>1</v>
       </c>
       <c r="E723" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.2">
@@ -12955,10 +12954,10 @@
         <v>66</v>
       </c>
       <c r="B724">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C724" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D724" t="b">
         <v>1</v>
@@ -12972,10 +12971,10 @@
         <v>66</v>
       </c>
       <c r="B725">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C725" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D725" t="b">
         <v>1</v>
@@ -12989,10 +12988,10 @@
         <v>66</v>
       </c>
       <c r="B726">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C726" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D726" t="b">
         <v>1</v>
@@ -13006,10 +13005,10 @@
         <v>66</v>
       </c>
       <c r="B727">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C727" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D727" t="b">
         <v>1</v>
@@ -13026,7 +13025,7 @@
         <v>2010</v>
       </c>
       <c r="C728" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D728" t="b">
         <v>1</v>
@@ -13043,7 +13042,7 @@
         <v>2010</v>
       </c>
       <c r="C729" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D729" t="b">
         <v>1</v>
@@ -13060,7 +13059,7 @@
         <v>2010</v>
       </c>
       <c r="C730" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D730" t="b">
         <v>1</v>
@@ -13077,7 +13076,7 @@
         <v>2010</v>
       </c>
       <c r="C731" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D731" t="b">
         <v>1</v>
@@ -13091,10 +13090,10 @@
         <v>66</v>
       </c>
       <c r="B732">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C732" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D732" t="b">
         <v>1</v>
@@ -13108,10 +13107,10 @@
         <v>66</v>
       </c>
       <c r="B733">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C733" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D733" t="b">
         <v>1</v>
@@ -13125,10 +13124,10 @@
         <v>66</v>
       </c>
       <c r="B734">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C734" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D734" t="b">
         <v>1</v>
@@ -13142,10 +13141,10 @@
         <v>66</v>
       </c>
       <c r="B735">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C735" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D735" t="b">
         <v>1</v>
@@ -13162,7 +13161,7 @@
         <v>2012</v>
       </c>
       <c r="C736" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D736" t="b">
         <v>1</v>
@@ -13179,7 +13178,7 @@
         <v>2012</v>
       </c>
       <c r="C737" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D737" t="b">
         <v>1</v>
@@ -13196,7 +13195,7 @@
         <v>2012</v>
       </c>
       <c r="C738" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D738" t="b">
         <v>1</v>
@@ -13213,7 +13212,7 @@
         <v>2012</v>
       </c>
       <c r="C739" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D739" t="b">
         <v>1</v>
@@ -13227,10 +13226,10 @@
         <v>66</v>
       </c>
       <c r="B740">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C740" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D740" t="b">
         <v>1</v>
@@ -13244,10 +13243,10 @@
         <v>66</v>
       </c>
       <c r="B741">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C741" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D741" t="b">
         <v>1</v>
@@ -13261,10 +13260,10 @@
         <v>66</v>
       </c>
       <c r="B742">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C742" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D742" t="b">
         <v>1</v>
@@ -13278,10 +13277,10 @@
         <v>66</v>
       </c>
       <c r="B743">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C743" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D743" t="b">
         <v>1</v>
@@ -13298,7 +13297,7 @@
         <v>2014</v>
       </c>
       <c r="C744" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D744" t="b">
         <v>1</v>
@@ -13315,7 +13314,7 @@
         <v>2014</v>
       </c>
       <c r="C745" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D745" t="b">
         <v>1</v>
@@ -13332,7 +13331,7 @@
         <v>2014</v>
       </c>
       <c r="C746" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D746" t="b">
         <v>1</v>
@@ -13349,7 +13348,7 @@
         <v>2014</v>
       </c>
       <c r="C747" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D747" t="b">
         <v>1</v>
@@ -13363,10 +13362,10 @@
         <v>66</v>
       </c>
       <c r="B748">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C748" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D748" t="b">
         <v>1</v>
@@ -13380,10 +13379,10 @@
         <v>66</v>
       </c>
       <c r="B749">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C749" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D749" t="b">
         <v>1</v>
@@ -13397,10 +13396,10 @@
         <v>66</v>
       </c>
       <c r="B750">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C750" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D750" t="b">
         <v>1</v>
@@ -13414,10 +13413,10 @@
         <v>66</v>
       </c>
       <c r="B751">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C751" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D751" t="b">
         <v>1</v>
@@ -13434,7 +13433,7 @@
         <v>2016</v>
       </c>
       <c r="C752" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D752" t="b">
         <v>1</v>
@@ -13451,7 +13450,7 @@
         <v>2016</v>
       </c>
       <c r="C753" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D753" t="b">
         <v>1</v>
@@ -13468,7 +13467,7 @@
         <v>2016</v>
       </c>
       <c r="C754" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D754" t="b">
         <v>1</v>
@@ -13485,7 +13484,7 @@
         <v>2016</v>
       </c>
       <c r="C755" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D755" t="b">
         <v>1</v>
@@ -13502,7 +13501,7 @@
         <v>2016</v>
       </c>
       <c r="C756" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D756" t="b">
         <v>1</v>
@@ -13519,7 +13518,7 @@
         <v>2016</v>
       </c>
       <c r="C757" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D757" t="b">
         <v>1</v>
@@ -13533,10 +13532,10 @@
         <v>66</v>
       </c>
       <c r="B758">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C758" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D758" t="b">
         <v>1</v>
@@ -13550,10 +13549,10 @@
         <v>66</v>
       </c>
       <c r="B759">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C759" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D759" t="b">
         <v>1</v>
@@ -13567,7 +13566,7 @@
         <v>66</v>
       </c>
       <c r="B760">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C760" t="s">
         <v>8</v>
@@ -13584,7 +13583,7 @@
         <v>66</v>
       </c>
       <c r="B761">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C761" t="s">
         <v>27</v>
@@ -13601,7 +13600,7 @@
         <v>66</v>
       </c>
       <c r="B762">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C762" t="s">
         <v>8</v>
@@ -13618,7 +13617,7 @@
         <v>66</v>
       </c>
       <c r="B763">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C763" t="s">
         <v>27</v>
@@ -13632,13 +13631,13 @@
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B764">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C764" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D764" t="b">
         <v>1</v>
@@ -13649,13 +13648,13 @@
     </row>
     <row r="765" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B765">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="C765" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D765" t="b">
         <v>1</v>
@@ -13666,13 +13665,13 @@
     </row>
     <row r="766" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B766">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C766" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D766" t="b">
         <v>1</v>
@@ -13683,13 +13682,13 @@
     </row>
     <row r="767" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B767">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C767" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D767" t="b">
         <v>1</v>
@@ -13703,7 +13702,7 @@
         <v>67</v>
       </c>
       <c r="B768">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C768" t="s">
         <v>9</v>
@@ -13720,7 +13719,7 @@
         <v>67</v>
       </c>
       <c r="B769">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C769" t="s">
         <v>14</v>
@@ -13737,7 +13736,7 @@
         <v>67</v>
       </c>
       <c r="B770">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C770" t="s">
         <v>10</v>
@@ -13754,7 +13753,7 @@
         <v>67</v>
       </c>
       <c r="B771">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C771" t="s">
         <v>13</v>
@@ -13771,7 +13770,7 @@
         <v>67</v>
       </c>
       <c r="B772">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C772" t="s">
         <v>9</v>
@@ -13788,7 +13787,7 @@
         <v>67</v>
       </c>
       <c r="B773">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C773" t="s">
         <v>14</v>
@@ -13802,13 +13801,13 @@
     </row>
     <row r="774" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B774">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C774" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D774" t="b">
         <v>1</v>
@@ -13819,13 +13818,13 @@
     </row>
     <row r="775" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B775">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C775" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D775" t="b">
         <v>1</v>
@@ -13836,13 +13835,13 @@
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B776">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C776" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D776" t="b">
         <v>1</v>
@@ -13853,13 +13852,13 @@
     </row>
     <row r="777" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B777">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C777" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D777" t="b">
         <v>1</v>
@@ -13873,7 +13872,7 @@
         <v>68</v>
       </c>
       <c r="B778">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C778" t="s">
         <v>9</v>
@@ -13890,7 +13889,7 @@
         <v>68</v>
       </c>
       <c r="B779">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C779" t="s">
         <v>14</v>
@@ -13907,7 +13906,7 @@
         <v>68</v>
       </c>
       <c r="B780">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C780" t="s">
         <v>10</v>
@@ -13924,7 +13923,7 @@
         <v>68</v>
       </c>
       <c r="B781">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C781" t="s">
         <v>13</v>
@@ -13938,10 +13937,10 @@
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B782">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C782" t="s">
         <v>9</v>
@@ -13955,10 +13954,10 @@
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B783">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C783" t="s">
         <v>14</v>
@@ -13972,10 +13971,10 @@
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B784">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C784" t="s">
         <v>10</v>
@@ -13989,10 +13988,10 @@
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B785">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C785" t="s">
         <v>13</v>
@@ -14009,7 +14008,7 @@
         <v>69</v>
       </c>
       <c r="B786">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C786" t="s">
         <v>9</v>
@@ -14026,7 +14025,7 @@
         <v>69</v>
       </c>
       <c r="B787">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C787" t="s">
         <v>14</v>
@@ -14043,7 +14042,7 @@
         <v>69</v>
       </c>
       <c r="B788">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C788" t="s">
         <v>10</v>
@@ -14060,7 +14059,7 @@
         <v>69</v>
       </c>
       <c r="B789">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C789" t="s">
         <v>13</v>
@@ -14074,10 +14073,10 @@
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B790">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C790" t="s">
         <v>9</v>
@@ -14086,15 +14085,15 @@
         <v>1</v>
       </c>
       <c r="E790" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B791">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C791" t="s">
         <v>14</v>
@@ -14103,41 +14102,41 @@
         <v>1</v>
       </c>
       <c r="E791" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B792">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C792" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D792" t="b">
         <v>1</v>
       </c>
       <c r="E792" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="793" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B793">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C793" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D793" t="b">
         <v>1</v>
       </c>
       <c r="E793" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.2">
@@ -14145,7 +14144,7 @@
         <v>70</v>
       </c>
       <c r="B794">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C794" t="s">
         <v>9</v>
@@ -14162,7 +14161,7 @@
         <v>70</v>
       </c>
       <c r="B795">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C795" t="s">
         <v>14</v>
@@ -14179,16 +14178,16 @@
         <v>70</v>
       </c>
       <c r="B796">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C796" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D796" t="b">
         <v>1</v>
       </c>
       <c r="E796" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.2">
@@ -14196,16 +14195,16 @@
         <v>70</v>
       </c>
       <c r="B797">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C797" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D797" t="b">
         <v>1</v>
       </c>
       <c r="E797" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.2">
@@ -14213,7 +14212,7 @@
         <v>70</v>
       </c>
       <c r="B798">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C798" t="s">
         <v>9</v>
@@ -14230,7 +14229,7 @@
         <v>70</v>
       </c>
       <c r="B799">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C799" t="s">
         <v>14</v>
@@ -14247,16 +14246,16 @@
         <v>70</v>
       </c>
       <c r="B800">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C800" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D800" t="b">
         <v>1</v>
       </c>
       <c r="E800" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.2">
@@ -14264,16 +14263,16 @@
         <v>70</v>
       </c>
       <c r="B801">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C801" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D801" t="b">
         <v>1</v>
       </c>
       <c r="E801" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.2">
@@ -14281,16 +14280,16 @@
         <v>70</v>
       </c>
       <c r="B802">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C802" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D802" t="b">
         <v>1</v>
       </c>
       <c r="E802" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.2">
@@ -14298,49 +14297,117 @@
         <v>70</v>
       </c>
       <c r="B803">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C803" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D803" t="b">
         <v>1</v>
       </c>
       <c r="E803" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B804">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C804" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D804" t="b">
         <v>1</v>
       </c>
       <c r="E804" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
+        <v>70</v>
+      </c>
+      <c r="B805">
+        <v>2016</v>
+      </c>
+      <c r="C805" t="s">
+        <v>14</v>
+      </c>
+      <c r="D805" t="b">
+        <v>1</v>
+      </c>
+      <c r="E805" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A806" t="s">
+        <v>70</v>
+      </c>
+      <c r="B806">
+        <v>2016</v>
+      </c>
+      <c r="C806" t="s">
+        <v>10</v>
+      </c>
+      <c r="D806" t="b">
+        <v>1</v>
+      </c>
+      <c r="E806" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A807" t="s">
+        <v>70</v>
+      </c>
+      <c r="B807">
+        <v>2016</v>
+      </c>
+      <c r="C807" t="s">
+        <v>13</v>
+      </c>
+      <c r="D807" t="b">
+        <v>1</v>
+      </c>
+      <c r="E807" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A808" t="s">
         <v>54</v>
       </c>
-      <c r="B805">
+      <c r="B808">
         <v>2022</v>
       </c>
-      <c r="C805" t="s">
-        <v>13</v>
-      </c>
-      <c r="D805" t="b">
-        <v>1</v>
-      </c>
-      <c r="E805" t="s">
+      <c r="C808" t="s">
+        <v>10</v>
+      </c>
+      <c r="D808" t="b">
+        <v>1</v>
+      </c>
+      <c r="E808" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A809" t="s">
+        <v>54</v>
+      </c>
+      <c r="B809">
+        <v>2022</v>
+      </c>
+      <c r="C809" t="s">
+        <v>13</v>
+      </c>
+      <c r="D809" t="b">
+        <v>1</v>
+      </c>
+      <c r="E809" t="s">
         <v>72</v>
       </c>
     </row>
@@ -14351,18 +14418,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:E1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62:K70">
-    <cfRule type="containsText" dxfId="1" priority="13" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",K62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="2" priority="14" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",K62)))</formula>
     </cfRule>
   </conditionalFormatting>
